--- a/Apr_17_DataValidationAssignment.xlsx
+++ b/Apr_17_DataValidationAssignment.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/378470feeb9e1e90/Desktop/data analytics templates/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pavit\OneDrive\Desktop\byte code assignment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="14_{633EE4D6-B246-4071-88CB-33DF51DE85B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8C69111B-310E-4061-B48F-43DF7D8D9987}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99F057F2-A477-44F7-AAF2-28E58AA2A308}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{CD87D0A8-DBF9-4512-BBA4-DA596FBA8524}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{CD87D0A8-DBF9-4512-BBA4-DA596FBA8524}"/>
   </bookViews>
   <sheets>
     <sheet name="Dataset" sheetId="2" r:id="rId1"/>
@@ -47,8 +47,9 @@
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
 <metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
+  <metadataTypes count="2">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
   <futureMetadata name="XLDAPR" count="1">
     <bk>
@@ -59,11 +60,25 @@
       </extLst>
     </bk>
   </futureMetadata>
+  <futureMetadata name="XLRICHVALUE" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
   <cellMetadata count="1">
     <bk>
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
+  <valueMetadata count="1">
+    <bk>
+      <rc t="2" v="0"/>
+    </bk>
+  </valueMetadata>
 </metadata>
 </file>
 
@@ -1133,7 +1148,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -1160,16 +1175,13 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1234,6 +1246,68 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
+<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
+  <global>
+    <keyFlags>
+      <key name="_Self">
+        <flag name="ExcludeFromFile" value="1"/>
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_DisplayString">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Flags">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Format">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_SubLabel">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Attribution">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Icon">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Display">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_CanonicalPropertyNames">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_ClassificationId">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+    </keyFlags>
+  </global>
+</rvTypesInfo>
+</file>
+
+<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <rv s="0">
+    <v>0</v>
+    <v>8</v>
+    <v>10</v>
+    <v>1</v>
+  </rv>
+</rvData>
+</file>
+
+<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <s t="_error">
+    <k n="colOffset" t="i"/>
+    <k n="errorType" t="i"/>
+    <k n="rwOffset" t="i"/>
+    <k n="subType" t="i"/>
+  </s>
+</rvStructures>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1617,54 +1691,54 @@
       </c>
     </row>
     <row r="3" spans="1:18">
-      <c r="A3" s="23" t="s">
+      <c r="A3" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="23" t="s">
+      <c r="B3" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="23" t="s">
+      <c r="C3" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="23" t="str">
+      <c r="D3" s="12" t="str">
         <f>PROPER(TRIM(C3))</f>
         <v>South</v>
       </c>
-      <c r="E3" s="23" t="s">
+      <c r="E3" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="23" t="s">
+      <c r="F3" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G3" s="23" t="s">
+      <c r="G3" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="H3" s="23">
+      <c r="H3" s="12">
         <v>33542</v>
       </c>
-      <c r="I3" s="23">
+      <c r="I3" s="12">
         <v>12954</v>
       </c>
-      <c r="J3" s="23" t="s">
+      <c r="J3" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="K3" s="23" t="s">
+      <c r="K3" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="L3" s="23" t="s">
+      <c r="L3" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="M3" s="23">
+      <c r="M3" s="12">
         <v>11</v>
       </c>
-      <c r="N3" s="23">
+      <c r="N3" s="12">
         <v>9473</v>
       </c>
-      <c r="O3" s="23" t="s">
+      <c r="O3" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="P3" s="23"/>
-      <c r="Q3" s="24" t="str">
+      <c r="P3" s="12"/>
+      <c r="Q3" t="str">
         <f>IF(H3&gt;I3,"Achived","Not Achieved")</f>
         <v>Achived</v>
       </c>
@@ -1674,56 +1748,56 @@
       </c>
     </row>
     <row r="4" spans="1:18">
-      <c r="A4" s="23" t="s">
+      <c r="A4" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="B4" s="23" t="s">
+      <c r="B4" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="C4" s="23" t="s">
+      <c r="C4" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="23" t="str">
+      <c r="D4" s="12" t="str">
         <f t="shared" ref="D4:D67" si="0">PROPER(TRIM(C4))</f>
         <v>West</v>
       </c>
-      <c r="E4" s="23" t="s">
+      <c r="E4" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="F4" s="23" t="s">
+      <c r="F4" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="G4" s="23" t="s">
+      <c r="G4" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="H4" s="23">
+      <c r="H4" s="12">
         <v>1695</v>
       </c>
-      <c r="I4" s="23">
+      <c r="I4" s="12">
         <v>12850</v>
       </c>
-      <c r="J4" s="23" t="s">
+      <c r="J4" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="K4" s="23" t="s">
+      <c r="K4" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="L4" s="23" t="s">
+      <c r="L4" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="M4" s="23">
+      <c r="M4" s="12">
         <v>0</v>
       </c>
-      <c r="N4" s="23">
+      <c r="N4" s="12">
         <v>7515</v>
       </c>
-      <c r="O4" s="23" t="s">
+      <c r="O4" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="P4" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q4" s="24" t="str">
+      <c r="P4" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q4" t="str">
         <f t="shared" ref="Q4:Q67" si="1">IF(H4&gt;I4,"Achived","Not Achieved")</f>
         <v>Not Achieved</v>
       </c>
@@ -1733,56 +1807,56 @@
       </c>
     </row>
     <row r="5" spans="1:18">
-      <c r="A5" s="23" t="s">
+      <c r="A5" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="23" t="s">
+      <c r="B5" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="C5" s="23" t="s">
+      <c r="C5" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="D5" s="23" t="str">
+      <c r="D5" s="12" t="str">
         <f t="shared" si="0"/>
         <v>North</v>
       </c>
-      <c r="E5" s="23" t="s">
+      <c r="E5" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="F5" s="23" t="s">
+      <c r="F5" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G5" s="23" t="s">
+      <c r="G5" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="H5" s="23">
+      <c r="H5" s="12">
         <v>32726</v>
       </c>
-      <c r="I5" s="23">
+      <c r="I5" s="12">
         <v>39638</v>
       </c>
-      <c r="J5" s="23" t="s">
+      <c r="J5" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="K5" s="23" t="s">
+      <c r="K5" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="L5" s="23" t="s">
+      <c r="L5" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="M5" s="23">
+      <c r="M5" s="12">
         <v>7</v>
       </c>
-      <c r="N5" s="23">
+      <c r="N5" s="12">
         <v>11860</v>
       </c>
-      <c r="O5" s="23" t="s">
+      <c r="O5" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="P5" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q5" s="24" t="str">
+      <c r="P5" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q5" t="str">
         <f t="shared" si="1"/>
         <v>Not Achieved</v>
       </c>
@@ -1792,56 +1866,56 @@
       </c>
     </row>
     <row r="6" spans="1:18">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="B6" s="23" t="s">
+      <c r="B6" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="C6" s="23" t="s">
+      <c r="C6" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="D6" s="23" t="str">
+      <c r="D6" s="12" t="str">
         <f t="shared" si="0"/>
         <v>North</v>
       </c>
-      <c r="E6" s="23" t="s">
+      <c r="E6" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="F6" s="23" t="s">
+      <c r="F6" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G6" s="23" t="s">
+      <c r="G6" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="H6" s="23">
+      <c r="H6" s="12">
         <v>55488</v>
       </c>
-      <c r="I6" s="23">
+      <c r="I6" s="12">
         <v>31119</v>
       </c>
-      <c r="J6" s="23" t="s">
+      <c r="J6" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="K6" s="23" t="s">
+      <c r="K6" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="L6" s="23" t="s">
+      <c r="L6" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="M6" s="23">
+      <c r="M6" s="12">
         <v>24</v>
       </c>
-      <c r="N6" s="23">
+      <c r="N6" s="12">
         <v>3382</v>
       </c>
-      <c r="O6" s="23" t="s">
+      <c r="O6" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="P6" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q6" s="24" t="str">
+      <c r="P6" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q6" t="str">
         <f t="shared" si="1"/>
         <v>Achived</v>
       </c>
@@ -1851,56 +1925,56 @@
       </c>
     </row>
     <row r="7" spans="1:18">
-      <c r="A7" s="23" t="s">
+      <c r="A7" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="B7" s="23" t="s">
+      <c r="B7" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="C7" s="23" t="s">
+      <c r="C7" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="D7" s="23" t="str">
+      <c r="D7" s="12" t="str">
         <f t="shared" si="0"/>
         <v>South</v>
       </c>
-      <c r="E7" s="23" t="s">
+      <c r="E7" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="F7" s="23" t="s">
+      <c r="F7" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="G7" s="23" t="s">
+      <c r="G7" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="H7" s="23">
+      <c r="H7" s="12">
         <v>6462</v>
       </c>
-      <c r="I7" s="23">
+      <c r="I7" s="12">
         <v>13904</v>
       </c>
-      <c r="J7" s="23" t="s">
+      <c r="J7" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="K7" s="23" t="s">
+      <c r="K7" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="L7" s="23" t="s">
+      <c r="L7" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="M7" s="23">
+      <c r="M7" s="12">
         <v>10</v>
       </c>
-      <c r="N7" s="23">
+      <c r="N7" s="12">
         <v>17486</v>
       </c>
-      <c r="O7" s="23" t="s">
+      <c r="O7" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="P7" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q7" s="24" t="str">
+      <c r="P7" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q7" t="str">
         <f t="shared" si="1"/>
         <v>Not Achieved</v>
       </c>
@@ -1910,56 +1984,56 @@
       </c>
     </row>
     <row r="8" spans="1:18">
-      <c r="A8" s="23" t="s">
+      <c r="A8" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="B8" s="23" t="s">
+      <c r="B8" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="C8" s="23" t="s">
+      <c r="C8" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="D8" s="23" t="str">
+      <c r="D8" s="12" t="str">
         <f t="shared" si="0"/>
         <v>East</v>
       </c>
-      <c r="E8" s="23" t="s">
+      <c r="E8" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="F8" s="23" t="s">
+      <c r="F8" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G8" s="23" t="s">
+      <c r="G8" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="H8" s="23">
+      <c r="H8" s="12">
         <v>19793</v>
       </c>
-      <c r="I8" s="23">
+      <c r="I8" s="12">
         <v>26195</v>
       </c>
-      <c r="J8" s="23" t="s">
+      <c r="J8" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="K8" s="23" t="s">
+      <c r="K8" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="L8" s="23" t="s">
+      <c r="L8" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="M8" s="23">
+      <c r="M8" s="12">
         <v>10</v>
       </c>
-      <c r="N8" s="23">
+      <c r="N8" s="12">
         <v>15604</v>
       </c>
-      <c r="O8" s="23" t="s">
+      <c r="O8" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="P8" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q8" s="24" t="str">
+      <c r="P8" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q8" t="str">
         <f t="shared" si="1"/>
         <v>Not Achieved</v>
       </c>
@@ -1969,56 +2043,56 @@
       </c>
     </row>
     <row r="9" spans="1:18">
-      <c r="A9" s="23" t="s">
+      <c r="A9" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="B9" s="23" t="s">
+      <c r="B9" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="C9" s="23" t="s">
+      <c r="C9" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="D9" s="23" t="str">
+      <c r="D9" s="12" t="str">
         <f t="shared" si="0"/>
         <v>East</v>
       </c>
-      <c r="E9" s="23" t="s">
+      <c r="E9" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="F9" s="23" t="s">
+      <c r="F9" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G9" s="23" t="s">
+      <c r="G9" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="H9" s="23">
+      <c r="H9" s="12">
         <v>3544</v>
       </c>
-      <c r="I9" s="23">
+      <c r="I9" s="12">
         <v>50234</v>
       </c>
-      <c r="J9" s="23" t="s">
+      <c r="J9" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="K9" s="23" t="s">
+      <c r="K9" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="L9" s="23" t="s">
+      <c r="L9" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="M9" s="23">
+      <c r="M9" s="12">
         <v>15</v>
       </c>
-      <c r="N9" s="23">
+      <c r="N9" s="12">
         <v>18676</v>
       </c>
-      <c r="O9" s="23" t="s">
+      <c r="O9" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="P9" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q9" s="24" t="str">
+      <c r="P9" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q9" t="str">
         <f t="shared" si="1"/>
         <v>Not Achieved</v>
       </c>
@@ -2028,56 +2102,56 @@
       </c>
     </row>
     <row r="10" spans="1:18">
-      <c r="A10" s="23" t="s">
+      <c r="A10" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="B10" s="23" t="s">
+      <c r="B10" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="C10" s="23" t="s">
+      <c r="C10" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="D10" s="23" t="str">
+      <c r="D10" s="12" t="str">
         <f t="shared" si="0"/>
         <v>North</v>
       </c>
-      <c r="E10" s="23" t="s">
+      <c r="E10" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="F10" s="23" t="s">
+      <c r="F10" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="G10" s="23" t="s">
+      <c r="G10" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="H10" s="23">
+      <c r="H10" s="12">
         <v>54687</v>
       </c>
-      <c r="I10" s="23">
+      <c r="I10" s="12">
         <v>33217</v>
       </c>
-      <c r="J10" s="23" t="s">
+      <c r="J10" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="K10" s="23" t="s">
+      <c r="K10" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="L10" s="23" t="s">
+      <c r="L10" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="M10" s="23">
+      <c r="M10" s="12">
         <v>23</v>
       </c>
-      <c r="N10" s="23">
+      <c r="N10" s="12">
         <v>2021</v>
       </c>
-      <c r="O10" s="23" t="s">
+      <c r="O10" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="P10" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q10" s="24" t="str">
+      <c r="P10" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q10" t="str">
         <f t="shared" si="1"/>
         <v>Achived</v>
       </c>
@@ -2087,56 +2161,56 @@
       </c>
     </row>
     <row r="11" spans="1:18">
-      <c r="A11" s="23" t="s">
+      <c r="A11" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="B11" s="23" t="s">
+      <c r="B11" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="C11" s="23" t="s">
+      <c r="C11" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="D11" s="23" t="str">
+      <c r="D11" s="12" t="str">
         <f t="shared" si="0"/>
         <v>South</v>
       </c>
-      <c r="E11" s="23" t="s">
+      <c r="E11" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="F11" s="23" t="s">
+      <c r="F11" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="G11" s="23" t="s">
+      <c r="G11" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="H11" s="23">
+      <c r="H11" s="12">
         <v>44295</v>
       </c>
-      <c r="I11" s="23">
+      <c r="I11" s="12">
         <v>43415</v>
       </c>
-      <c r="J11" s="23" t="s">
+      <c r="J11" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="K11" s="23" t="s">
+      <c r="K11" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="L11" s="23" t="s">
+      <c r="L11" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="M11" s="23">
+      <c r="M11" s="12">
         <v>6</v>
       </c>
-      <c r="N11" s="23">
+      <c r="N11" s="12">
         <v>12029</v>
       </c>
-      <c r="O11" s="23" t="s">
+      <c r="O11" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="P11" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q11" s="24" t="str">
+      <c r="P11" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q11" t="str">
         <f t="shared" si="1"/>
         <v>Achived</v>
       </c>
@@ -2146,56 +2220,56 @@
       </c>
     </row>
     <row r="12" spans="1:18">
-      <c r="A12" s="23" t="s">
+      <c r="A12" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="23" t="s">
+      <c r="B12" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="C12" s="23" t="s">
+      <c r="C12" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D12" s="23" t="str">
+      <c r="D12" s="12" t="str">
         <f t="shared" si="0"/>
         <v>South</v>
       </c>
-      <c r="E12" s="23" t="s">
+      <c r="E12" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="F12" s="23" t="s">
+      <c r="F12" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="G12" s="23" t="s">
+      <c r="G12" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="H12" s="23">
+      <c r="H12" s="12">
         <v>28873</v>
       </c>
-      <c r="I12" s="23">
+      <c r="I12" s="12">
         <v>12516</v>
       </c>
-      <c r="J12" s="23" t="s">
+      <c r="J12" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="K12" s="23" t="s">
+      <c r="K12" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="L12" s="23" t="s">
+      <c r="L12" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="M12" s="23">
+      <c r="M12" s="12">
         <v>4</v>
       </c>
-      <c r="N12" s="23">
+      <c r="N12" s="12">
         <v>7256</v>
       </c>
-      <c r="O12" s="23" t="s">
+      <c r="O12" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="P12" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q12" s="24" t="str">
+      <c r="P12" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q12" t="str">
         <f t="shared" si="1"/>
         <v>Achived</v>
       </c>
@@ -2205,54 +2279,54 @@
       </c>
     </row>
     <row r="13" spans="1:18">
-      <c r="A13" s="23" t="s">
+      <c r="A13" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="B13" s="23" t="s">
+      <c r="B13" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="C13" s="23" t="s">
+      <c r="C13" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="D13" s="23" t="str">
+      <c r="D13" s="12" t="str">
         <f t="shared" si="0"/>
         <v>North</v>
       </c>
-      <c r="E13" s="23" t="s">
+      <c r="E13" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="F13" s="23" t="s">
+      <c r="F13" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G13" s="23" t="s">
+      <c r="G13" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="H13" s="23">
+      <c r="H13" s="12">
         <v>69667</v>
       </c>
-      <c r="I13" s="23">
+      <c r="I13" s="12">
         <v>30909</v>
       </c>
-      <c r="J13" s="23" t="s">
+      <c r="J13" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="K13" s="23" t="s">
+      <c r="K13" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="L13" s="23" t="s">
+      <c r="L13" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="M13" s="23">
+      <c r="M13" s="12">
         <v>20</v>
       </c>
-      <c r="N13" s="23">
+      <c r="N13" s="12">
         <v>6281</v>
       </c>
-      <c r="O13" s="23" t="s">
+      <c r="O13" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="P13" s="23"/>
-      <c r="Q13" s="24" t="str">
+      <c r="P13" s="12"/>
+      <c r="Q13" t="str">
         <f t="shared" si="1"/>
         <v>Achived</v>
       </c>
@@ -2262,56 +2336,56 @@
       </c>
     </row>
     <row r="14" spans="1:18">
-      <c r="A14" s="23" t="s">
+      <c r="A14" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="B14" s="23" t="s">
+      <c r="B14" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="C14" s="23" t="s">
+      <c r="C14" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="D14" s="23" t="str">
+      <c r="D14" s="12" t="str">
         <f t="shared" si="0"/>
         <v>North</v>
       </c>
-      <c r="E14" s="23" t="s">
+      <c r="E14" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="F14" s="23" t="s">
+      <c r="F14" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="G14" s="23" t="s">
+      <c r="G14" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="H14" s="23">
+      <c r="H14" s="12">
         <v>31649</v>
       </c>
-      <c r="I14" s="23">
+      <c r="I14" s="12">
         <v>20150</v>
       </c>
-      <c r="J14" s="23" t="s">
+      <c r="J14" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="K14" s="23" t="s">
+      <c r="K14" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="L14" s="23" t="s">
+      <c r="L14" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="M14" s="23">
+      <c r="M14" s="12">
         <v>24</v>
       </c>
-      <c r="N14" s="23">
+      <c r="N14" s="12">
         <v>6431</v>
       </c>
-      <c r="O14" s="23" t="s">
+      <c r="O14" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="P14" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q14" s="24" t="str">
+      <c r="P14" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q14" t="str">
         <f t="shared" si="1"/>
         <v>Achived</v>
       </c>
@@ -2321,56 +2395,56 @@
       </c>
     </row>
     <row r="15" spans="1:18">
-      <c r="A15" s="23" t="s">
+      <c r="A15" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="B15" s="23" t="s">
+      <c r="B15" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="C15" s="23" t="s">
+      <c r="C15" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D15" s="23" t="str">
+      <c r="D15" s="12" t="str">
         <f t="shared" si="0"/>
         <v>South</v>
       </c>
-      <c r="E15" s="23" t="s">
+      <c r="E15" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="F15" s="23" t="s">
+      <c r="F15" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="G15" s="23" t="s">
+      <c r="G15" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="H15" s="23">
+      <c r="H15" s="12">
         <v>12387</v>
       </c>
-      <c r="I15" s="23">
+      <c r="I15" s="12">
         <v>14593</v>
       </c>
-      <c r="J15" s="23" t="s">
+      <c r="J15" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="K15" s="23" t="s">
+      <c r="K15" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="L15" s="23" t="s">
+      <c r="L15" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="M15" s="23">
+      <c r="M15" s="12">
         <v>6</v>
       </c>
-      <c r="N15" s="23">
+      <c r="N15" s="12">
         <v>-349</v>
       </c>
-      <c r="O15" s="23" t="s">
+      <c r="O15" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="P15" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q15" s="24" t="str">
+      <c r="P15" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q15" t="str">
         <f t="shared" si="1"/>
         <v>Not Achieved</v>
       </c>
@@ -2380,56 +2454,56 @@
       </c>
     </row>
     <row r="16" spans="1:18">
-      <c r="A16" s="23" t="s">
+      <c r="A16" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="B16" s="23" t="s">
+      <c r="B16" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="C16" s="23" t="s">
+      <c r="C16" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D16" s="23" t="str">
+      <c r="D16" s="12" t="str">
         <f t="shared" si="0"/>
         <v>South</v>
       </c>
-      <c r="E16" s="23" t="s">
+      <c r="E16" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="F16" s="23" t="s">
+      <c r="F16" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="G16" s="23" t="s">
+      <c r="G16" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="H16" s="23">
+      <c r="H16" s="12">
         <v>26099</v>
       </c>
-      <c r="I16" s="23">
+      <c r="I16" s="12">
         <v>31119</v>
       </c>
-      <c r="J16" s="23" t="s">
+      <c r="J16" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="K16" s="23" t="s">
+      <c r="K16" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="L16" s="23" t="s">
+      <c r="L16" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="M16" s="23">
+      <c r="M16" s="12">
         <v>25</v>
       </c>
-      <c r="N16" s="23">
+      <c r="N16" s="12">
         <v>15161</v>
       </c>
-      <c r="O16" s="23" t="s">
+      <c r="O16" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="P16" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q16" s="24" t="str">
+      <c r="P16" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q16" t="str">
         <f t="shared" si="1"/>
         <v>Not Achieved</v>
       </c>
@@ -2439,56 +2513,56 @@
       </c>
     </row>
     <row r="17" spans="1:18">
-      <c r="A17" s="23" t="s">
+      <c r="A17" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="B17" s="23" t="s">
+      <c r="B17" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="C17" s="23" t="s">
+      <c r="C17" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="D17" s="23" t="str">
+      <c r="D17" s="12" t="str">
         <f t="shared" si="0"/>
         <v>South</v>
       </c>
-      <c r="E17" s="23" t="s">
+      <c r="E17" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="F17" s="23" t="s">
+      <c r="F17" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G17" s="23" t="s">
+      <c r="G17" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="H17" s="23">
+      <c r="H17" s="12">
         <v>19360</v>
       </c>
-      <c r="I17" s="23">
+      <c r="I17" s="12">
         <v>30437</v>
       </c>
-      <c r="J17" s="23" t="s">
+      <c r="J17" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="K17" s="23" t="s">
+      <c r="K17" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="L17" s="23" t="s">
+      <c r="L17" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="M17" s="23">
+      <c r="M17" s="12">
         <v>13</v>
       </c>
-      <c r="N17" s="23">
+      <c r="N17" s="12">
         <v>8440</v>
       </c>
-      <c r="O17" s="23" t="s">
+      <c r="O17" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="P17" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q17" s="24" t="str">
+      <c r="P17" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q17" t="str">
         <f t="shared" si="1"/>
         <v>Not Achieved</v>
       </c>
@@ -2498,54 +2572,54 @@
       </c>
     </row>
     <row r="18" spans="1:18">
-      <c r="A18" s="23" t="s">
+      <c r="A18" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="B18" s="23" t="s">
+      <c r="B18" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="C18" s="23" t="s">
+      <c r="C18" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="D18" s="23" t="str">
+      <c r="D18" s="12" t="str">
         <f t="shared" si="0"/>
         <v>South</v>
       </c>
-      <c r="E18" s="23" t="s">
+      <c r="E18" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="F18" s="23" t="s">
+      <c r="F18" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G18" s="23" t="s">
+      <c r="G18" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="H18" s="23">
+      <c r="H18" s="12">
         <v>47964</v>
       </c>
-      <c r="I18" s="23">
+      <c r="I18" s="12">
         <v>11359</v>
       </c>
-      <c r="J18" s="23" t="s">
+      <c r="J18" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="K18" s="23" t="s">
+      <c r="K18" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="L18" s="23" t="s">
+      <c r="L18" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="M18" s="23">
+      <c r="M18" s="12">
         <v>20</v>
       </c>
-      <c r="N18" s="23">
+      <c r="N18" s="12">
         <v>3298</v>
       </c>
-      <c r="O18" s="23" t="s">
+      <c r="O18" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="P18" s="23"/>
-      <c r="Q18" s="24" t="str">
+      <c r="P18" s="12"/>
+      <c r="Q18" t="str">
         <f t="shared" si="1"/>
         <v>Achived</v>
       </c>
@@ -2555,56 +2629,56 @@
       </c>
     </row>
     <row r="19" spans="1:18">
-      <c r="A19" s="23" t="s">
+      <c r="A19" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="B19" s="23" t="s">
+      <c r="B19" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="C19" s="23" t="s">
+      <c r="C19" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="D19" s="23" t="str">
+      <c r="D19" s="12" t="str">
         <f t="shared" si="0"/>
         <v>North</v>
       </c>
-      <c r="E19" s="23" t="s">
+      <c r="E19" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="F19" s="23" t="s">
+      <c r="F19" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G19" s="23" t="s">
+      <c r="G19" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="H19" s="23">
+      <c r="H19" s="12">
         <v>64906</v>
       </c>
-      <c r="I19" s="23">
+      <c r="I19" s="12">
         <v>22941</v>
       </c>
-      <c r="J19" s="23" t="s">
+      <c r="J19" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="K19" s="23" t="s">
+      <c r="K19" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="L19" s="23" t="s">
+      <c r="L19" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="M19" s="23">
+      <c r="M19" s="12">
         <v>11</v>
       </c>
-      <c r="N19" s="23">
+      <c r="N19" s="12">
         <v>56</v>
       </c>
-      <c r="O19" s="23" t="s">
+      <c r="O19" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="P19" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q19" s="24" t="str">
+      <c r="P19" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q19" t="str">
         <f t="shared" si="1"/>
         <v>Achived</v>
       </c>
@@ -2614,56 +2688,56 @@
       </c>
     </row>
     <row r="20" spans="1:18">
-      <c r="A20" s="23" t="s">
+      <c r="A20" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="B20" s="23" t="s">
+      <c r="B20" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="C20" s="23" t="s">
+      <c r="C20" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="D20" s="23" t="str">
+      <c r="D20" s="12" t="str">
         <f t="shared" si="0"/>
         <v>North</v>
       </c>
-      <c r="E20" s="23" t="s">
+      <c r="E20" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="F20" s="23" t="s">
+      <c r="F20" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="G20" s="23" t="s">
+      <c r="G20" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="H20" s="23">
+      <c r="H20" s="12">
         <v>18761</v>
       </c>
-      <c r="I20" s="23">
+      <c r="I20" s="12">
         <v>47837</v>
       </c>
-      <c r="J20" s="23" t="s">
+      <c r="J20" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="K20" s="23" t="s">
+      <c r="K20" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="L20" s="23" t="s">
+      <c r="L20" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="M20" s="23">
+      <c r="M20" s="12">
         <v>29</v>
       </c>
-      <c r="N20" s="23">
+      <c r="N20" s="12">
         <v>-1459</v>
       </c>
-      <c r="O20" s="23" t="s">
+      <c r="O20" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="P20" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q20" s="24" t="str">
+      <c r="P20" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q20" t="str">
         <f t="shared" si="1"/>
         <v>Not Achieved</v>
       </c>
@@ -2673,54 +2747,54 @@
       </c>
     </row>
     <row r="21" spans="1:18">
-      <c r="A21" s="23" t="s">
+      <c r="A21" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="B21" s="23" t="s">
+      <c r="B21" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="C21" s="23" t="s">
+      <c r="C21" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="D21" s="23" t="str">
+      <c r="D21" s="12" t="str">
         <f t="shared" si="0"/>
         <v>South</v>
       </c>
-      <c r="E21" s="23" t="s">
+      <c r="E21" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="F21" s="23" t="s">
+      <c r="F21" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="G21" s="23" t="s">
+      <c r="G21" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="H21" s="23">
+      <c r="H21" s="12">
         <v>29729</v>
       </c>
-      <c r="I21" s="23">
+      <c r="I21" s="12">
         <v>22997</v>
       </c>
-      <c r="J21" s="23" t="s">
+      <c r="J21" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="K21" s="23" t="s">
+      <c r="K21" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="L21" s="23" t="s">
+      <c r="L21" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="M21" s="23">
+      <c r="M21" s="12">
         <v>28</v>
       </c>
-      <c r="N21" s="23">
+      <c r="N21" s="12">
         <v>11944</v>
       </c>
-      <c r="O21" s="23" t="s">
+      <c r="O21" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="P21" s="23"/>
-      <c r="Q21" s="24" t="str">
+      <c r="P21" s="12"/>
+      <c r="Q21" t="str">
         <f t="shared" si="1"/>
         <v>Achived</v>
       </c>
@@ -2730,56 +2804,56 @@
       </c>
     </row>
     <row r="22" spans="1:18">
-      <c r="A22" s="23" t="s">
+      <c r="A22" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="B22" s="23" t="s">
+      <c r="B22" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="C22" s="23" t="s">
+      <c r="C22" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="D22" s="23" t="str">
+      <c r="D22" s="12" t="str">
         <f t="shared" si="0"/>
         <v>East</v>
       </c>
-      <c r="E22" s="23" t="s">
+      <c r="E22" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="F22" s="23" t="s">
+      <c r="F22" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="G22" s="23" t="s">
+      <c r="G22" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="H22" s="23">
+      <c r="H22" s="12">
         <v>54227</v>
       </c>
-      <c r="I22" s="23">
+      <c r="I22" s="12">
         <v>31452</v>
       </c>
-      <c r="J22" s="23" t="s">
+      <c r="J22" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="K22" s="23" t="s">
+      <c r="K22" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="L22" s="23" t="s">
+      <c r="L22" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="M22" s="23">
+      <c r="M22" s="12">
         <v>11</v>
       </c>
-      <c r="N22" s="23">
+      <c r="N22" s="12">
         <v>3069</v>
       </c>
-      <c r="O22" s="23" t="s">
+      <c r="O22" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="P22" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q22" s="24" t="str">
+      <c r="P22" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q22" t="str">
         <f t="shared" si="1"/>
         <v>Achived</v>
       </c>
@@ -2789,56 +2863,56 @@
       </c>
     </row>
     <row r="23" spans="1:18">
-      <c r="A23" s="23" t="s">
+      <c r="A23" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="B23" s="23" t="s">
+      <c r="B23" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="C23" s="23" t="s">
+      <c r="C23" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="D23" s="23" t="str">
+      <c r="D23" s="12" t="str">
         <f t="shared" si="0"/>
         <v>South</v>
       </c>
-      <c r="E23" s="23" t="s">
+      <c r="E23" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="F23" s="23" t="s">
+      <c r="F23" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G23" s="23" t="s">
+      <c r="G23" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="H23" s="23">
+      <c r="H23" s="12">
         <v>1472</v>
       </c>
-      <c r="I23" s="23">
+      <c r="I23" s="12">
         <v>40535</v>
       </c>
-      <c r="J23" s="23" t="s">
+      <c r="J23" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="K23" s="23" t="s">
+      <c r="K23" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="L23" s="23" t="s">
+      <c r="L23" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="M23" s="23">
+      <c r="M23" s="12">
         <v>22</v>
       </c>
-      <c r="N23" s="23">
+      <c r="N23" s="12">
         <v>3351</v>
       </c>
-      <c r="O23" s="23" t="s">
+      <c r="O23" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="P23" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q23" s="24" t="str">
+      <c r="P23" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q23" t="str">
         <f t="shared" si="1"/>
         <v>Not Achieved</v>
       </c>
@@ -2848,56 +2922,56 @@
       </c>
     </row>
     <row r="24" spans="1:18">
-      <c r="A24" s="23" t="s">
+      <c r="A24" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="B24" s="23" t="s">
+      <c r="B24" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="C24" s="23" t="s">
+      <c r="C24" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="D24" s="23" t="str">
+      <c r="D24" s="12" t="str">
         <f t="shared" si="0"/>
         <v>West</v>
       </c>
-      <c r="E24" s="23" t="s">
+      <c r="E24" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="F24" s="23" t="s">
+      <c r="F24" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="G24" s="23" t="s">
+      <c r="G24" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="H24" s="23">
+      <c r="H24" s="12">
         <v>45574</v>
       </c>
-      <c r="I24" s="23">
+      <c r="I24" s="12">
         <v>26722</v>
       </c>
-      <c r="J24" s="23" t="s">
+      <c r="J24" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="K24" s="23" t="s">
+      <c r="K24" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="L24" s="23" t="s">
+      <c r="L24" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="M24" s="23">
+      <c r="M24" s="12">
         <v>28</v>
       </c>
-      <c r="N24" s="23">
+      <c r="N24" s="12">
         <v>13313</v>
       </c>
-      <c r="O24" s="23" t="s">
+      <c r="O24" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="P24" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q24" s="24" t="str">
+      <c r="P24" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q24" t="str">
         <f t="shared" si="1"/>
         <v>Achived</v>
       </c>
@@ -2907,56 +2981,56 @@
       </c>
     </row>
     <row r="25" spans="1:18">
-      <c r="A25" s="23" t="s">
+      <c r="A25" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="B25" s="23" t="s">
+      <c r="B25" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="C25" s="23" t="s">
+      <c r="C25" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="D25" s="23" t="str">
+      <c r="D25" s="12" t="str">
         <f t="shared" si="0"/>
         <v>South</v>
       </c>
-      <c r="E25" s="23" t="s">
+      <c r="E25" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="F25" s="23" t="s">
+      <c r="F25" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G25" s="23" t="s">
+      <c r="G25" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="H25" s="23">
+      <c r="H25" s="12">
         <v>18965</v>
       </c>
-      <c r="I25" s="23">
+      <c r="I25" s="12">
         <v>58750</v>
       </c>
-      <c r="J25" s="23" t="s">
+      <c r="J25" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="K25" s="23" t="s">
+      <c r="K25" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="L25" s="23" t="s">
+      <c r="L25" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="M25" s="23">
+      <c r="M25" s="12">
         <v>4</v>
       </c>
-      <c r="N25" s="23">
+      <c r="N25" s="12">
         <v>1622</v>
       </c>
-      <c r="O25" s="23" t="s">
+      <c r="O25" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="P25" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q25" s="24" t="str">
+      <c r="P25" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q25" t="str">
         <f t="shared" si="1"/>
         <v>Not Achieved</v>
       </c>
@@ -2966,54 +3040,54 @@
       </c>
     </row>
     <row r="26" spans="1:18">
-      <c r="A26" s="23" t="s">
+      <c r="A26" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="B26" s="23" t="s">
+      <c r="B26" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="C26" s="23" t="s">
+      <c r="C26" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D26" s="23" t="str">
+      <c r="D26" s="12" t="str">
         <f t="shared" si="0"/>
         <v>South</v>
       </c>
-      <c r="E26" s="23" t="s">
+      <c r="E26" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="F26" s="23" t="s">
+      <c r="F26" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="G26" s="23" t="s">
+      <c r="G26" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="H26" s="23">
+      <c r="H26" s="12">
         <v>10975</v>
       </c>
-      <c r="I26" s="23">
+      <c r="I26" s="12">
         <v>43232</v>
       </c>
-      <c r="J26" s="23" t="s">
+      <c r="J26" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="K26" s="23" t="s">
+      <c r="K26" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="L26" s="23" t="s">
+      <c r="L26" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="M26" s="23">
+      <c r="M26" s="12">
         <v>27</v>
       </c>
-      <c r="N26" s="23">
+      <c r="N26" s="12">
         <v>15688</v>
       </c>
-      <c r="O26" s="23" t="s">
+      <c r="O26" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="P26" s="23"/>
-      <c r="Q26" s="24" t="str">
+      <c r="P26" s="12"/>
+      <c r="Q26" t="str">
         <f t="shared" si="1"/>
         <v>Not Achieved</v>
       </c>
@@ -3023,56 +3097,56 @@
       </c>
     </row>
     <row r="27" spans="1:18">
-      <c r="A27" s="23" t="s">
+      <c r="A27" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="B27" s="23" t="s">
+      <c r="B27" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="C27" s="23" t="s">
+      <c r="C27" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="D27" s="23" t="str">
+      <c r="D27" s="12" t="str">
         <f t="shared" si="0"/>
         <v>South</v>
       </c>
-      <c r="E27" s="23" t="s">
+      <c r="E27" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="F27" s="23" t="s">
+      <c r="F27" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="G27" s="23" t="s">
+      <c r="G27" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="H27" s="23">
+      <c r="H27" s="12">
         <v>63714</v>
       </c>
-      <c r="I27" s="23">
+      <c r="I27" s="12">
         <v>33030</v>
       </c>
-      <c r="J27" s="23" t="s">
+      <c r="J27" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="K27" s="23" t="s">
+      <c r="K27" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="L27" s="23" t="s">
+      <c r="L27" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="M27" s="23">
+      <c r="M27" s="12">
         <v>17</v>
       </c>
-      <c r="N27" s="23">
+      <c r="N27" s="12">
         <v>14152</v>
       </c>
-      <c r="O27" s="23" t="s">
+      <c r="O27" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="P27" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q27" s="24" t="str">
+      <c r="P27" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q27" t="str">
         <f t="shared" si="1"/>
         <v>Achived</v>
       </c>
@@ -3082,56 +3156,56 @@
       </c>
     </row>
     <row r="28" spans="1:18">
-      <c r="A28" s="23" t="s">
+      <c r="A28" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="B28" s="23" t="s">
+      <c r="B28" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="C28" s="23" t="s">
+      <c r="C28" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="D28" s="23" t="str">
+      <c r="D28" s="12" t="str">
         <f t="shared" si="0"/>
         <v>East</v>
       </c>
-      <c r="E28" s="23" t="s">
+      <c r="E28" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="F28" s="23" t="s">
+      <c r="F28" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="G28" s="23" t="s">
+      <c r="G28" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="H28" s="23">
+      <c r="H28" s="12">
         <v>21464</v>
       </c>
-      <c r="I28" s="23">
+      <c r="I28" s="12">
         <v>14424</v>
       </c>
-      <c r="J28" s="23" t="s">
+      <c r="J28" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="K28" s="23" t="s">
+      <c r="K28" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="L28" s="23" t="s">
+      <c r="L28" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="M28" s="23">
+      <c r="M28" s="12">
         <v>14</v>
       </c>
-      <c r="N28" s="23">
+      <c r="N28" s="12">
         <v>-176</v>
       </c>
-      <c r="O28" s="23" t="s">
+      <c r="O28" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="P28" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q28" s="24" t="str">
+      <c r="P28" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q28" t="str">
         <f t="shared" si="1"/>
         <v>Achived</v>
       </c>
@@ -3141,56 +3215,56 @@
       </c>
     </row>
     <row r="29" spans="1:18">
-      <c r="A29" s="23" t="s">
+      <c r="A29" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="B29" s="23" t="s">
+      <c r="B29" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="C29" s="23" t="s">
+      <c r="C29" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="D29" s="23" t="str">
+      <c r="D29" s="12" t="str">
         <f t="shared" si="0"/>
         <v>South</v>
       </c>
-      <c r="E29" s="23" t="s">
+      <c r="E29" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="F29" s="23" t="s">
+      <c r="F29" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G29" s="23" t="s">
+      <c r="G29" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="H29" s="23">
+      <c r="H29" s="12">
         <v>69681</v>
       </c>
-      <c r="I29" s="23">
+      <c r="I29" s="12">
         <v>22709</v>
       </c>
-      <c r="J29" s="23" t="s">
+      <c r="J29" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="K29" s="23" t="s">
+      <c r="K29" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="L29" s="23" t="s">
+      <c r="L29" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="M29" s="23">
+      <c r="M29" s="12">
         <v>22</v>
       </c>
-      <c r="N29" s="23">
+      <c r="N29" s="12">
         <v>11220</v>
       </c>
-      <c r="O29" s="23" t="s">
+      <c r="O29" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="P29" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q29" s="24" t="str">
+      <c r="P29" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q29" t="str">
         <f t="shared" si="1"/>
         <v>Achived</v>
       </c>
@@ -3200,56 +3274,56 @@
       </c>
     </row>
     <row r="30" spans="1:18">
-      <c r="A30" s="23" t="s">
+      <c r="A30" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="B30" s="23" t="s">
+      <c r="B30" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="C30" s="23" t="s">
+      <c r="C30" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="D30" s="23" t="str">
+      <c r="D30" s="12" t="str">
         <f t="shared" si="0"/>
         <v>South</v>
       </c>
-      <c r="E30" s="23" t="s">
+      <c r="E30" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="F30" s="23" t="s">
+      <c r="F30" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="G30" s="23" t="s">
+      <c r="G30" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="H30" s="23">
+      <c r="H30" s="12">
         <v>12605</v>
       </c>
-      <c r="I30" s="23">
+      <c r="I30" s="12">
         <v>52898</v>
       </c>
-      <c r="J30" s="23" t="s">
+      <c r="J30" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="K30" s="23" t="s">
+      <c r="K30" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="L30" s="23" t="s">
+      <c r="L30" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="M30" s="23">
+      <c r="M30" s="12">
         <v>22</v>
       </c>
-      <c r="N30" s="23">
+      <c r="N30" s="12">
         <v>9282</v>
       </c>
-      <c r="O30" s="23" t="s">
+      <c r="O30" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="P30" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q30" s="24" t="str">
+      <c r="P30" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q30" t="str">
         <f t="shared" si="1"/>
         <v>Not Achieved</v>
       </c>
@@ -3259,56 +3333,56 @@
       </c>
     </row>
     <row r="31" spans="1:18">
-      <c r="A31" s="23" t="s">
+      <c r="A31" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="B31" s="23" t="s">
+      <c r="B31" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="C31" s="23" t="s">
+      <c r="C31" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="D31" s="23" t="str">
+      <c r="D31" s="12" t="str">
         <f t="shared" si="0"/>
         <v>South</v>
       </c>
-      <c r="E31" s="23" t="s">
+      <c r="E31" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="F31" s="23" t="s">
+      <c r="F31" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G31" s="23" t="s">
+      <c r="G31" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="H31" s="23">
+      <c r="H31" s="12">
         <v>34166</v>
       </c>
-      <c r="I31" s="23">
+      <c r="I31" s="12">
         <v>10787</v>
       </c>
-      <c r="J31" s="23" t="s">
+      <c r="J31" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="K31" s="23" t="s">
+      <c r="K31" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="L31" s="23" t="s">
+      <c r="L31" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="M31" s="23">
+      <c r="M31" s="12">
         <v>0</v>
       </c>
-      <c r="N31" s="23">
+      <c r="N31" s="12">
         <v>3413</v>
       </c>
-      <c r="O31" s="23" t="s">
+      <c r="O31" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="P31" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q31" s="24" t="str">
+      <c r="P31" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q31" t="str">
         <f t="shared" si="1"/>
         <v>Achived</v>
       </c>
@@ -3318,56 +3392,56 @@
       </c>
     </row>
     <row r="32" spans="1:18">
-      <c r="A32" s="23" t="s">
+      <c r="A32" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="B32" s="23" t="s">
+      <c r="B32" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="C32" s="23" t="s">
+      <c r="C32" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="D32" s="23" t="str">
+      <c r="D32" s="12" t="str">
         <f t="shared" si="0"/>
         <v>South</v>
       </c>
-      <c r="E32" s="23" t="s">
+      <c r="E32" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="F32" s="23" t="s">
+      <c r="F32" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G32" s="23" t="s">
+      <c r="G32" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="H32" s="23">
+      <c r="H32" s="12">
         <v>3697</v>
       </c>
-      <c r="I32" s="23">
+      <c r="I32" s="12">
         <v>45050</v>
       </c>
-      <c r="J32" s="23" t="s">
+      <c r="J32" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="K32" s="23" t="s">
+      <c r="K32" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="L32" s="23" t="s">
+      <c r="L32" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="M32" s="23">
+      <c r="M32" s="12">
         <v>10</v>
       </c>
-      <c r="N32" s="23">
+      <c r="N32" s="12">
         <v>4772</v>
       </c>
-      <c r="O32" s="23" t="s">
+      <c r="O32" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="P32" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q32" s="24" t="str">
+      <c r="P32" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q32" t="str">
         <f t="shared" si="1"/>
         <v>Not Achieved</v>
       </c>
@@ -3377,56 +3451,56 @@
       </c>
     </row>
     <row r="33" spans="1:18">
-      <c r="A33" s="23" t="s">
+      <c r="A33" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="B33" s="23" t="s">
+      <c r="B33" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="C33" s="23" t="s">
+      <c r="C33" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="D33" s="23" t="str">
+      <c r="D33" s="12" t="str">
         <f t="shared" si="0"/>
         <v>South</v>
       </c>
-      <c r="E33" s="23" t="s">
+      <c r="E33" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="F33" s="23" t="s">
+      <c r="F33" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="G33" s="23" t="s">
+      <c r="G33" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="H33" s="23">
+      <c r="H33" s="12">
         <v>46409</v>
       </c>
-      <c r="I33" s="23">
+      <c r="I33" s="12">
         <v>51668</v>
       </c>
-      <c r="J33" s="23" t="s">
+      <c r="J33" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="K33" s="23" t="s">
+      <c r="K33" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="L33" s="23" t="s">
+      <c r="L33" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="M33" s="23">
+      <c r="M33" s="12">
         <v>12</v>
       </c>
-      <c r="N33" s="23">
+      <c r="N33" s="12">
         <v>17512</v>
       </c>
-      <c r="O33" s="23" t="s">
+      <c r="O33" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="P33" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q33" s="24" t="str">
+      <c r="P33" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q33" t="str">
         <f t="shared" si="1"/>
         <v>Not Achieved</v>
       </c>
@@ -3436,56 +3510,56 @@
       </c>
     </row>
     <row r="34" spans="1:18">
-      <c r="A34" s="23" t="s">
+      <c r="A34" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="B34" s="23" t="s">
+      <c r="B34" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="C34" s="23" t="s">
+      <c r="C34" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="D34" s="23" t="str">
+      <c r="D34" s="12" t="str">
         <f t="shared" si="0"/>
         <v>South</v>
       </c>
-      <c r="E34" s="23" t="s">
+      <c r="E34" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="F34" s="23" t="s">
+      <c r="F34" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="G34" s="23" t="s">
+      <c r="G34" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="H34" s="23">
+      <c r="H34" s="12">
         <v>4453</v>
       </c>
-      <c r="I34" s="23">
+      <c r="I34" s="12">
         <v>59934</v>
       </c>
-      <c r="J34" s="23" t="s">
+      <c r="J34" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="K34" s="23" t="s">
+      <c r="K34" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="L34" s="23" t="s">
+      <c r="L34" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="M34" s="23">
+      <c r="M34" s="12">
         <v>6</v>
       </c>
-      <c r="N34" s="23">
+      <c r="N34" s="12">
         <v>2331</v>
       </c>
-      <c r="O34" s="23" t="s">
+      <c r="O34" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="P34" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q34" s="24" t="str">
+      <c r="P34" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q34" t="str">
         <f t="shared" si="1"/>
         <v>Not Achieved</v>
       </c>
@@ -3495,54 +3569,54 @@
       </c>
     </row>
     <row r="35" spans="1:18">
-      <c r="A35" s="23" t="s">
+      <c r="A35" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="B35" s="23" t="s">
+      <c r="B35" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="C35" s="23" t="s">
+      <c r="C35" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="D35" s="23" t="str">
+      <c r="D35" s="12" t="str">
         <f t="shared" si="0"/>
         <v>South</v>
       </c>
-      <c r="E35" s="23" t="s">
+      <c r="E35" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="F35" s="23" t="s">
+      <c r="F35" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G35" s="23" t="s">
+      <c r="G35" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="H35" s="23">
+      <c r="H35" s="12">
         <v>59611</v>
       </c>
-      <c r="I35" s="23">
+      <c r="I35" s="12">
         <v>36782</v>
       </c>
-      <c r="J35" s="23" t="s">
+      <c r="J35" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="K35" s="23" t="s">
+      <c r="K35" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="L35" s="23" t="s">
+      <c r="L35" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="M35" s="23">
+      <c r="M35" s="12">
         <v>2</v>
       </c>
-      <c r="N35" s="23">
+      <c r="N35" s="12">
         <v>4048</v>
       </c>
-      <c r="O35" s="23" t="s">
+      <c r="O35" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="P35" s="23"/>
-      <c r="Q35" s="24" t="str">
+      <c r="P35" s="12"/>
+      <c r="Q35" t="str">
         <f t="shared" si="1"/>
         <v>Achived</v>
       </c>
@@ -3552,56 +3626,56 @@
       </c>
     </row>
     <row r="36" spans="1:18">
-      <c r="A36" s="23" t="s">
+      <c r="A36" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="B36" s="23" t="s">
+      <c r="B36" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="C36" s="23" t="s">
+      <c r="C36" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="D36" s="23" t="str">
+      <c r="D36" s="12" t="str">
         <f t="shared" si="0"/>
         <v>South</v>
       </c>
-      <c r="E36" s="23" t="s">
+      <c r="E36" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="F36" s="23" t="s">
+      <c r="F36" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G36" s="23" t="s">
+      <c r="G36" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="H36" s="23">
+      <c r="H36" s="12">
         <v>56703</v>
       </c>
-      <c r="I36" s="23">
+      <c r="I36" s="12">
         <v>31586</v>
       </c>
-      <c r="J36" s="23" t="s">
+      <c r="J36" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="K36" s="23" t="s">
+      <c r="K36" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="L36" s="23" t="s">
+      <c r="L36" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="M36" s="23">
+      <c r="M36" s="12">
         <v>1</v>
       </c>
-      <c r="N36" s="23">
+      <c r="N36" s="12">
         <v>10550</v>
       </c>
-      <c r="O36" s="23" t="s">
+      <c r="O36" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="P36" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q36" s="24" t="str">
+      <c r="P36" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q36" t="str">
         <f t="shared" si="1"/>
         <v>Achived</v>
       </c>
@@ -3611,56 +3685,56 @@
       </c>
     </row>
     <row r="37" spans="1:18">
-      <c r="A37" s="23" t="s">
+      <c r="A37" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="B37" s="23" t="s">
+      <c r="B37" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="C37" s="23" t="s">
+      <c r="C37" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="D37" s="23" t="str">
+      <c r="D37" s="12" t="str">
         <f t="shared" si="0"/>
         <v>West</v>
       </c>
-      <c r="E37" s="23" t="s">
+      <c r="E37" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="F37" s="23" t="s">
+      <c r="F37" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G37" s="23" t="s">
+      <c r="G37" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="H37" s="23">
+      <c r="H37" s="12">
         <v>12056</v>
       </c>
-      <c r="I37" s="23">
+      <c r="I37" s="12">
         <v>39141</v>
       </c>
-      <c r="J37" s="23" t="s">
+      <c r="J37" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="K37" s="23" t="s">
+      <c r="K37" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="L37" s="23" t="s">
+      <c r="L37" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="M37" s="23">
+      <c r="M37" s="12">
         <v>6</v>
       </c>
-      <c r="N37" s="23">
+      <c r="N37" s="12">
         <v>5056</v>
       </c>
-      <c r="O37" s="23" t="s">
+      <c r="O37" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="P37" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q37" s="24" t="str">
+      <c r="P37" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q37" t="str">
         <f t="shared" si="1"/>
         <v>Not Achieved</v>
       </c>
@@ -3670,56 +3744,56 @@
       </c>
     </row>
     <row r="38" spans="1:18">
-      <c r="A38" s="23" t="s">
+      <c r="A38" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="B38" s="23" t="s">
+      <c r="B38" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="C38" s="23" t="s">
+      <c r="C38" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="D38" s="23" t="str">
+      <c r="D38" s="12" t="str">
         <f t="shared" si="0"/>
         <v>West</v>
       </c>
-      <c r="E38" s="23" t="s">
+      <c r="E38" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="F38" s="23" t="s">
+      <c r="F38" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="G38" s="23" t="s">
+      <c r="G38" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="H38" s="23">
+      <c r="H38" s="12">
         <v>51048</v>
       </c>
-      <c r="I38" s="23">
+      <c r="I38" s="12">
         <v>36832</v>
       </c>
-      <c r="J38" s="23" t="s">
+      <c r="J38" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="K38" s="23" t="s">
+      <c r="K38" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="L38" s="23" t="s">
+      <c r="L38" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="M38" s="23">
+      <c r="M38" s="12">
         <v>20</v>
       </c>
-      <c r="N38" s="23">
+      <c r="N38" s="12">
         <v>2841</v>
       </c>
-      <c r="O38" s="23" t="s">
+      <c r="O38" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="P38" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q38" s="24" t="str">
+      <c r="P38" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q38" t="str">
         <f t="shared" si="1"/>
         <v>Achived</v>
       </c>
@@ -3729,56 +3803,56 @@
       </c>
     </row>
     <row r="39" spans="1:18">
-      <c r="A39" s="23" t="s">
+      <c r="A39" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="B39" s="23" t="s">
+      <c r="B39" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="C39" s="23" t="s">
+      <c r="C39" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="D39" s="23" t="str">
+      <c r="D39" s="12" t="str">
         <f t="shared" si="0"/>
         <v>South</v>
       </c>
-      <c r="E39" s="23" t="s">
+      <c r="E39" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="F39" s="23" t="s">
+      <c r="F39" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="G39" s="23" t="s">
+      <c r="G39" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="H39" s="23">
+      <c r="H39" s="12">
         <v>57071</v>
       </c>
-      <c r="I39" s="23">
+      <c r="I39" s="12">
         <v>11650</v>
       </c>
-      <c r="J39" s="23" t="s">
+      <c r="J39" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="K39" s="23" t="s">
+      <c r="K39" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="L39" s="23" t="s">
+      <c r="L39" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="M39" s="23">
+      <c r="M39" s="12">
         <v>21</v>
       </c>
-      <c r="N39" s="23">
+      <c r="N39" s="12">
         <v>2721</v>
       </c>
-      <c r="O39" s="23" t="s">
+      <c r="O39" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="P39" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q39" s="24" t="str">
+      <c r="P39" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q39" t="str">
         <f t="shared" si="1"/>
         <v>Achived</v>
       </c>
@@ -3788,56 +3862,56 @@
       </c>
     </row>
     <row r="40" spans="1:18">
-      <c r="A40" s="23" t="s">
+      <c r="A40" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="B40" s="23" t="s">
+      <c r="B40" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="C40" s="23" t="s">
+      <c r="C40" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="D40" s="23" t="str">
+      <c r="D40" s="12" t="str">
         <f t="shared" si="0"/>
         <v>West</v>
       </c>
-      <c r="E40" s="23" t="s">
+      <c r="E40" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="F40" s="23" t="s">
+      <c r="F40" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="G40" s="23" t="s">
+      <c r="G40" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="H40" s="23">
+      <c r="H40" s="12">
         <v>49502</v>
       </c>
-      <c r="I40" s="23">
+      <c r="I40" s="12">
         <v>49632</v>
       </c>
-      <c r="J40" s="23" t="s">
+      <c r="J40" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="K40" s="23" t="s">
+      <c r="K40" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="L40" s="23" t="s">
+      <c r="L40" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="M40" s="23">
+      <c r="M40" s="12">
         <v>12</v>
       </c>
-      <c r="N40" s="23">
+      <c r="N40" s="12">
         <v>14588</v>
       </c>
-      <c r="O40" s="23" t="s">
+      <c r="O40" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="P40" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q40" s="24" t="str">
+      <c r="P40" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q40" t="str">
         <f t="shared" si="1"/>
         <v>Not Achieved</v>
       </c>
@@ -3847,56 +3921,56 @@
       </c>
     </row>
     <row r="41" spans="1:18">
-      <c r="A41" s="23" t="s">
+      <c r="A41" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="B41" s="23" t="s">
+      <c r="B41" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="C41" s="23" t="s">
+      <c r="C41" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="D41" s="23" t="str">
+      <c r="D41" s="12" t="str">
         <f t="shared" si="0"/>
         <v>South</v>
       </c>
-      <c r="E41" s="23" t="s">
+      <c r="E41" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="F41" s="23" t="s">
+      <c r="F41" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G41" s="23" t="s">
+      <c r="G41" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="H41" s="23">
+      <c r="H41" s="12">
         <v>58914</v>
       </c>
-      <c r="I41" s="23">
+      <c r="I41" s="12">
         <v>41016</v>
       </c>
-      <c r="J41" s="23" t="s">
+      <c r="J41" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="K41" s="23" t="s">
+      <c r="K41" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="L41" s="23" t="s">
+      <c r="L41" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="M41" s="23">
+      <c r="M41" s="12">
         <v>30</v>
       </c>
-      <c r="N41" s="23">
+      <c r="N41" s="12">
         <v>14974</v>
       </c>
-      <c r="O41" s="23" t="s">
+      <c r="O41" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="P41" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q41" s="24" t="str">
+      <c r="P41" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q41" t="str">
         <f t="shared" si="1"/>
         <v>Achived</v>
       </c>
@@ -3906,56 +3980,56 @@
       </c>
     </row>
     <row r="42" spans="1:18">
-      <c r="A42" s="23" t="s">
+      <c r="A42" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="B42" s="23" t="s">
+      <c r="B42" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="C42" s="23" t="s">
+      <c r="C42" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="D42" s="23" t="str">
+      <c r="D42" s="12" t="str">
         <f t="shared" si="0"/>
         <v>West</v>
       </c>
-      <c r="E42" s="23" t="s">
+      <c r="E42" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="F42" s="23" t="s">
+      <c r="F42" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="G42" s="23" t="s">
+      <c r="G42" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="H42" s="23">
+      <c r="H42" s="12">
         <v>42423</v>
       </c>
-      <c r="I42" s="23">
+      <c r="I42" s="12">
         <v>52142</v>
       </c>
-      <c r="J42" s="23" t="s">
+      <c r="J42" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="K42" s="23" t="s">
+      <c r="K42" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="L42" s="23" t="s">
+      <c r="L42" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="M42" s="23">
+      <c r="M42" s="12">
         <v>9</v>
       </c>
-      <c r="N42" s="23">
+      <c r="N42" s="12">
         <v>17435</v>
       </c>
-      <c r="O42" s="23" t="s">
+      <c r="O42" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="P42" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q42" s="24" t="str">
+      <c r="P42" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q42" t="str">
         <f t="shared" si="1"/>
         <v>Not Achieved</v>
       </c>
@@ -3965,56 +4039,56 @@
       </c>
     </row>
     <row r="43" spans="1:18">
-      <c r="A43" s="23" t="s">
+      <c r="A43" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="B43" s="23" t="s">
+      <c r="B43" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="C43" s="23" t="s">
+      <c r="C43" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D43" s="23" t="str">
+      <c r="D43" s="12" t="str">
         <f t="shared" si="0"/>
         <v>South</v>
       </c>
-      <c r="E43" s="23" t="s">
+      <c r="E43" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="F43" s="23" t="s">
+      <c r="F43" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="G43" s="23" t="s">
+      <c r="G43" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="H43" s="23">
+      <c r="H43" s="12">
         <v>24307</v>
       </c>
-      <c r="I43" s="23">
+      <c r="I43" s="12">
         <v>27329</v>
       </c>
-      <c r="J43" s="23" t="s">
+      <c r="J43" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="K43" s="23" t="s">
+      <c r="K43" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="L43" s="23" t="s">
+      <c r="L43" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="M43" s="23">
+      <c r="M43" s="12">
         <v>8</v>
       </c>
-      <c r="N43" s="23">
+      <c r="N43" s="12">
         <v>-660</v>
       </c>
-      <c r="O43" s="23" t="s">
+      <c r="O43" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="P43" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q43" s="24" t="str">
+      <c r="P43" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q43" t="str">
         <f t="shared" si="1"/>
         <v>Not Achieved</v>
       </c>
@@ -4024,56 +4098,56 @@
       </c>
     </row>
     <row r="44" spans="1:18">
-      <c r="A44" s="23" t="s">
+      <c r="A44" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="B44" s="23" t="s">
+      <c r="B44" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="C44" s="23" t="s">
+      <c r="C44" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="D44" s="23" t="str">
+      <c r="D44" s="12" t="str">
         <f t="shared" si="0"/>
         <v>South</v>
       </c>
-      <c r="E44" s="23" t="s">
+      <c r="E44" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="F44" s="23" t="s">
+      <c r="F44" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="G44" s="23" t="s">
+      <c r="G44" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="H44" s="23">
+      <c r="H44" s="12">
         <v>43081</v>
       </c>
-      <c r="I44" s="23">
+      <c r="I44" s="12">
         <v>14741</v>
       </c>
-      <c r="J44" s="23" t="s">
+      <c r="J44" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="K44" s="23" t="s">
+      <c r="K44" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="L44" s="23" t="s">
+      <c r="L44" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="M44" s="23">
+      <c r="M44" s="12">
         <v>14</v>
       </c>
-      <c r="N44" s="23">
+      <c r="N44" s="12">
         <v>8081</v>
       </c>
-      <c r="O44" s="23" t="s">
+      <c r="O44" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="P44" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q44" s="24" t="str">
+      <c r="P44" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q44" t="str">
         <f t="shared" si="1"/>
         <v>Achived</v>
       </c>
@@ -4083,56 +4157,56 @@
       </c>
     </row>
     <row r="45" spans="1:18">
-      <c r="A45" s="23" t="s">
+      <c r="A45" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="B45" s="23" t="s">
+      <c r="B45" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="C45" s="23" t="s">
+      <c r="C45" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="D45" s="23" t="str">
+      <c r="D45" s="12" t="str">
         <f t="shared" si="0"/>
         <v>South</v>
       </c>
-      <c r="E45" s="23" t="s">
+      <c r="E45" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="F45" s="23" t="s">
+      <c r="F45" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="G45" s="23" t="s">
+      <c r="G45" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="H45" s="23">
+      <c r="H45" s="12">
         <v>38833</v>
       </c>
-      <c r="I45" s="23">
+      <c r="I45" s="12">
         <v>11508</v>
       </c>
-      <c r="J45" s="23" t="s">
+      <c r="J45" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="K45" s="23" t="s">
+      <c r="K45" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="L45" s="23" t="s">
+      <c r="L45" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="M45" s="23">
+      <c r="M45" s="12">
         <v>6</v>
       </c>
-      <c r="N45" s="23">
+      <c r="N45" s="12">
         <v>7077</v>
       </c>
-      <c r="O45" s="23" t="s">
+      <c r="O45" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="P45" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q45" s="24" t="str">
+      <c r="P45" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q45" t="str">
         <f t="shared" si="1"/>
         <v>Achived</v>
       </c>
@@ -4142,56 +4216,56 @@
       </c>
     </row>
     <row r="46" spans="1:18">
-      <c r="A46" s="23" t="s">
+      <c r="A46" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="B46" s="23" t="s">
+      <c r="B46" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="C46" s="23" t="s">
+      <c r="C46" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="D46" s="23" t="str">
+      <c r="D46" s="12" t="str">
         <f t="shared" si="0"/>
         <v>South</v>
       </c>
-      <c r="E46" s="23" t="s">
+      <c r="E46" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="F46" s="23" t="s">
+      <c r="F46" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="G46" s="23" t="s">
+      <c r="G46" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="H46" s="23">
+      <c r="H46" s="12">
         <v>66337</v>
       </c>
-      <c r="I46" s="23">
+      <c r="I46" s="12">
         <v>31809</v>
       </c>
-      <c r="J46" s="23" t="s">
+      <c r="J46" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="K46" s="23" t="s">
+      <c r="K46" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="L46" s="23" t="s">
+      <c r="L46" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="M46" s="23">
+      <c r="M46" s="12">
         <v>9</v>
       </c>
-      <c r="N46" s="23">
+      <c r="N46" s="12">
         <v>19440</v>
       </c>
-      <c r="O46" s="23" t="s">
+      <c r="O46" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="P46" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q46" s="24" t="str">
+      <c r="P46" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q46" t="str">
         <f t="shared" si="1"/>
         <v>Achived</v>
       </c>
@@ -4201,56 +4275,56 @@
       </c>
     </row>
     <row r="47" spans="1:18">
-      <c r="A47" s="23" t="s">
+      <c r="A47" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="B47" s="23" t="s">
+      <c r="B47" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="C47" s="23" t="s">
+      <c r="C47" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="D47" s="23" t="str">
+      <c r="D47" s="12" t="str">
         <f t="shared" si="0"/>
         <v>West</v>
       </c>
-      <c r="E47" s="23" t="s">
+      <c r="E47" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="F47" s="23" t="s">
+      <c r="F47" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G47" s="23" t="s">
+      <c r="G47" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="H47" s="23">
+      <c r="H47" s="12">
         <v>6659</v>
       </c>
-      <c r="I47" s="23">
+      <c r="I47" s="12">
         <v>47528</v>
       </c>
-      <c r="J47" s="23" t="s">
+      <c r="J47" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="K47" s="23" t="s">
+      <c r="K47" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="L47" s="23" t="s">
+      <c r="L47" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="M47" s="23">
+      <c r="M47" s="12">
         <v>25</v>
       </c>
-      <c r="N47" s="23">
+      <c r="N47" s="12">
         <v>6743</v>
       </c>
-      <c r="O47" s="23" t="s">
+      <c r="O47" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="P47" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q47" s="24" t="str">
+      <c r="P47" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q47" t="str">
         <f t="shared" si="1"/>
         <v>Not Achieved</v>
       </c>
@@ -4260,56 +4334,56 @@
       </c>
     </row>
     <row r="48" spans="1:18">
-      <c r="A48" s="23" t="s">
+      <c r="A48" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="B48" s="23" t="s">
+      <c r="B48" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="C48" s="23" t="s">
+      <c r="C48" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="D48" s="23" t="str">
+      <c r="D48" s="12" t="str">
         <f t="shared" si="0"/>
         <v>South</v>
       </c>
-      <c r="E48" s="23" t="s">
+      <c r="E48" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="F48" s="23" t="s">
+      <c r="F48" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="G48" s="23" t="s">
+      <c r="G48" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="H48" s="23">
+      <c r="H48" s="12">
         <v>9054</v>
       </c>
-      <c r="I48" s="23">
+      <c r="I48" s="12">
         <v>25204</v>
       </c>
-      <c r="J48" s="23" t="s">
+      <c r="J48" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="K48" s="23" t="s">
+      <c r="K48" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="L48" s="23" t="s">
+      <c r="L48" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="M48" s="23">
+      <c r="M48" s="12">
         <v>6</v>
       </c>
-      <c r="N48" s="23">
+      <c r="N48" s="12">
         <v>1413</v>
       </c>
-      <c r="O48" s="23" t="s">
+      <c r="O48" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="P48" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q48" s="24" t="str">
+      <c r="P48" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q48" t="str">
         <f t="shared" si="1"/>
         <v>Not Achieved</v>
       </c>
@@ -4319,56 +4393,56 @@
       </c>
     </row>
     <row r="49" spans="1:18">
-      <c r="A49" s="23" t="s">
+      <c r="A49" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="B49" s="23" t="s">
+      <c r="B49" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="C49" s="23" t="s">
+      <c r="C49" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="D49" s="23" t="str">
+      <c r="D49" s="12" t="str">
         <f t="shared" si="0"/>
         <v>North</v>
       </c>
-      <c r="E49" s="23" t="s">
+      <c r="E49" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="F49" s="23" t="s">
+      <c r="F49" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="G49" s="23" t="s">
+      <c r="G49" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="H49" s="23">
+      <c r="H49" s="12">
         <v>14782</v>
       </c>
-      <c r="I49" s="23">
+      <c r="I49" s="12">
         <v>29349</v>
       </c>
-      <c r="J49" s="23" t="s">
+      <c r="J49" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="K49" s="23" t="s">
+      <c r="K49" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="L49" s="23" t="s">
+      <c r="L49" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="M49" s="23">
+      <c r="M49" s="12">
         <v>11</v>
       </c>
-      <c r="N49" s="23">
+      <c r="N49" s="12">
         <v>2373</v>
       </c>
-      <c r="O49" s="23" t="s">
+      <c r="O49" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="P49" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q49" s="24" t="str">
+      <c r="P49" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q49" t="str">
         <f t="shared" si="1"/>
         <v>Not Achieved</v>
       </c>
@@ -4378,56 +4452,56 @@
       </c>
     </row>
     <row r="50" spans="1:18">
-      <c r="A50" s="23" t="s">
+      <c r="A50" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="B50" s="23" t="s">
+      <c r="B50" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="C50" s="23" t="s">
+      <c r="C50" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="D50" s="23" t="str">
+      <c r="D50" s="12" t="str">
         <f t="shared" si="0"/>
         <v>South</v>
       </c>
-      <c r="E50" s="23" t="s">
+      <c r="E50" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="F50" s="23" t="s">
+      <c r="F50" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G50" s="23" t="s">
+      <c r="G50" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="H50" s="23">
+      <c r="H50" s="12">
         <v>69784</v>
       </c>
-      <c r="I50" s="23">
+      <c r="I50" s="12">
         <v>27605</v>
       </c>
-      <c r="J50" s="23" t="s">
+      <c r="J50" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="K50" s="23" t="s">
+      <c r="K50" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="L50" s="23" t="s">
+      <c r="L50" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="M50" s="23">
+      <c r="M50" s="12">
         <v>0</v>
       </c>
-      <c r="N50" s="23">
+      <c r="N50" s="12">
         <v>7546</v>
       </c>
-      <c r="O50" s="23" t="s">
+      <c r="O50" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="P50" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q50" s="24" t="str">
+      <c r="P50" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q50" t="str">
         <f t="shared" si="1"/>
         <v>Achived</v>
       </c>
@@ -4437,56 +4511,56 @@
       </c>
     </row>
     <row r="51" spans="1:18">
-      <c r="A51" s="23" t="s">
+      <c r="A51" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="B51" s="23" t="s">
+      <c r="B51" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="C51" s="23" t="s">
+      <c r="C51" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="D51" s="23" t="str">
+      <c r="D51" s="12" t="str">
         <f t="shared" si="0"/>
         <v>North</v>
       </c>
-      <c r="E51" s="23" t="s">
+      <c r="E51" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="F51" s="23" t="s">
+      <c r="F51" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G51" s="23" t="s">
+      <c r="G51" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="H51" s="23">
+      <c r="H51" s="12">
         <v>37570</v>
       </c>
-      <c r="I51" s="23">
+      <c r="I51" s="12">
         <v>21892</v>
       </c>
-      <c r="J51" s="23" t="s">
+      <c r="J51" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="K51" s="23" t="s">
+      <c r="K51" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="L51" s="23" t="s">
+      <c r="L51" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="M51" s="23">
+      <c r="M51" s="12">
         <v>20</v>
       </c>
-      <c r="N51" s="23">
+      <c r="N51" s="12">
         <v>12965</v>
       </c>
-      <c r="O51" s="23" t="s">
+      <c r="O51" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="P51" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q51" s="24" t="str">
+      <c r="P51" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q51" t="str">
         <f t="shared" si="1"/>
         <v>Achived</v>
       </c>
@@ -4496,56 +4570,56 @@
       </c>
     </row>
     <row r="52" spans="1:18">
-      <c r="A52" s="23" t="s">
+      <c r="A52" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="B52" s="23" t="s">
+      <c r="B52" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="C52" s="23" t="s">
+      <c r="C52" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="D52" s="23" t="str">
+      <c r="D52" s="12" t="str">
         <f t="shared" si="0"/>
         <v>South</v>
       </c>
-      <c r="E52" s="23" t="s">
+      <c r="E52" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="F52" s="23" t="s">
+      <c r="F52" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G52" s="23" t="s">
+      <c r="G52" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="H52" s="23">
+      <c r="H52" s="12">
         <v>55300</v>
       </c>
-      <c r="I52" s="23">
+      <c r="I52" s="12">
         <v>30675</v>
       </c>
-      <c r="J52" s="23" t="s">
+      <c r="J52" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="K52" s="23" t="s">
+      <c r="K52" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="L52" s="23" t="s">
+      <c r="L52" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="M52" s="23">
+      <c r="M52" s="12">
         <v>22</v>
       </c>
-      <c r="N52" s="23">
+      <c r="N52" s="12">
         <v>4375</v>
       </c>
-      <c r="O52" s="23" t="s">
+      <c r="O52" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="P52" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q52" s="24" t="str">
+      <c r="P52" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q52" t="str">
         <f t="shared" si="1"/>
         <v>Achived</v>
       </c>
@@ -4555,56 +4629,56 @@
       </c>
     </row>
     <row r="53" spans="1:18">
-      <c r="A53" s="23" t="s">
+      <c r="A53" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="B53" s="23" t="s">
+      <c r="B53" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="C53" s="23" t="s">
+      <c r="C53" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="D53" s="23" t="str">
+      <c r="D53" s="12" t="str">
         <f t="shared" si="0"/>
         <v>South</v>
       </c>
-      <c r="E53" s="23" t="s">
+      <c r="E53" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="F53" s="23" t="s">
+      <c r="F53" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G53" s="23" t="s">
+      <c r="G53" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="H53" s="23">
+      <c r="H53" s="12">
         <v>29245</v>
       </c>
-      <c r="I53" s="23">
+      <c r="I53" s="12">
         <v>36897</v>
       </c>
-      <c r="J53" s="23" t="s">
+      <c r="J53" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="K53" s="23" t="s">
+      <c r="K53" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="L53" s="23" t="s">
+      <c r="L53" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="M53" s="23">
+      <c r="M53" s="12">
         <v>25</v>
       </c>
-      <c r="N53" s="23">
+      <c r="N53" s="12">
         <v>15755</v>
       </c>
-      <c r="O53" s="23" t="s">
+      <c r="O53" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="P53" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q53" s="24" t="str">
+      <c r="P53" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q53" t="str">
         <f t="shared" si="1"/>
         <v>Not Achieved</v>
       </c>
@@ -4614,54 +4688,54 @@
       </c>
     </row>
     <row r="54" spans="1:18">
-      <c r="A54" s="23" t="s">
+      <c r="A54" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="B54" s="23" t="s">
+      <c r="B54" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="C54" s="23" t="s">
+      <c r="C54" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="D54" s="23" t="str">
+      <c r="D54" s="12" t="str">
         <f t="shared" si="0"/>
         <v>South</v>
       </c>
-      <c r="E54" s="23" t="s">
+      <c r="E54" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="F54" s="23" t="s">
+      <c r="F54" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G54" s="23" t="s">
+      <c r="G54" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="H54" s="23">
+      <c r="H54" s="12">
         <v>189</v>
       </c>
-      <c r="I54" s="23">
+      <c r="I54" s="12">
         <v>49748</v>
       </c>
-      <c r="J54" s="23" t="s">
+      <c r="J54" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="K54" s="23" t="s">
+      <c r="K54" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="L54" s="23" t="s">
+      <c r="L54" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="M54" s="23">
+      <c r="M54" s="12">
         <v>8</v>
       </c>
-      <c r="N54" s="23">
+      <c r="N54" s="12">
         <v>10799</v>
       </c>
-      <c r="O54" s="23" t="s">
+      <c r="O54" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="P54" s="23"/>
-      <c r="Q54" s="24" t="str">
+      <c r="P54" s="12"/>
+      <c r="Q54" t="str">
         <f t="shared" si="1"/>
         <v>Not Achieved</v>
       </c>
@@ -4671,56 +4745,56 @@
       </c>
     </row>
     <row r="55" spans="1:18">
-      <c r="A55" s="23" t="s">
+      <c r="A55" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="B55" s="23" t="s">
+      <c r="B55" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="C55" s="23" t="s">
+      <c r="C55" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="D55" s="23" t="str">
+      <c r="D55" s="12" t="str">
         <f t="shared" si="0"/>
         <v>West</v>
       </c>
-      <c r="E55" s="23" t="s">
+      <c r="E55" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="F55" s="23" t="s">
+      <c r="F55" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="G55" s="23" t="s">
+      <c r="G55" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="H55" s="23">
+      <c r="H55" s="12">
         <v>65349</v>
       </c>
-      <c r="I55" s="23">
+      <c r="I55" s="12">
         <v>57387</v>
       </c>
-      <c r="J55" s="23" t="s">
+      <c r="J55" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="K55" s="23" t="s">
+      <c r="K55" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="L55" s="23" t="s">
+      <c r="L55" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="M55" s="23">
+      <c r="M55" s="12">
         <v>14</v>
       </c>
-      <c r="N55" s="23">
+      <c r="N55" s="12">
         <v>14449</v>
       </c>
-      <c r="O55" s="23" t="s">
+      <c r="O55" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="P55" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q55" s="24" t="str">
+      <c r="P55" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q55" t="str">
         <f t="shared" si="1"/>
         <v>Achived</v>
       </c>
@@ -4730,54 +4804,54 @@
       </c>
     </row>
     <row r="56" spans="1:18">
-      <c r="A56" s="23" t="s">
+      <c r="A56" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="B56" s="23" t="s">
+      <c r="B56" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="C56" s="23" t="s">
+      <c r="C56" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="D56" s="23" t="str">
+      <c r="D56" s="12" t="str">
         <f t="shared" si="0"/>
         <v>South</v>
       </c>
-      <c r="E56" s="23" t="s">
+      <c r="E56" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="F56" s="23" t="s">
+      <c r="F56" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="G56" s="23" t="s">
+      <c r="G56" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="H56" s="23">
+      <c r="H56" s="12">
         <v>69387</v>
       </c>
-      <c r="I56" s="23">
+      <c r="I56" s="12">
         <v>10168</v>
       </c>
-      <c r="J56" s="23" t="s">
+      <c r="J56" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="K56" s="23" t="s">
+      <c r="K56" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="L56" s="23" t="s">
+      <c r="L56" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="M56" s="23">
+      <c r="M56" s="12">
         <v>12</v>
       </c>
-      <c r="N56" s="23">
+      <c r="N56" s="12">
         <v>-28</v>
       </c>
-      <c r="O56" s="23" t="s">
+      <c r="O56" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="P56" s="23"/>
-      <c r="Q56" s="24" t="str">
+      <c r="P56" s="12"/>
+      <c r="Q56" t="str">
         <f t="shared" si="1"/>
         <v>Achived</v>
       </c>
@@ -4787,56 +4861,56 @@
       </c>
     </row>
     <row r="57" spans="1:18">
-      <c r="A57" s="23" t="s">
+      <c r="A57" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="B57" s="23" t="s">
+      <c r="B57" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="C57" s="23" t="s">
+      <c r="C57" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="D57" s="23" t="str">
+      <c r="D57" s="12" t="str">
         <f t="shared" si="0"/>
         <v>East</v>
       </c>
-      <c r="E57" s="23" t="s">
+      <c r="E57" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="F57" s="23" t="s">
+      <c r="F57" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="G57" s="23" t="s">
+      <c r="G57" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="H57" s="23">
+      <c r="H57" s="12">
         <v>32013</v>
       </c>
-      <c r="I57" s="23">
+      <c r="I57" s="12">
         <v>14862</v>
       </c>
-      <c r="J57" s="23" t="s">
+      <c r="J57" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="K57" s="23" t="s">
+      <c r="K57" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="L57" s="23" t="s">
+      <c r="L57" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="M57" s="23">
+      <c r="M57" s="12">
         <v>12</v>
       </c>
-      <c r="N57" s="23">
+      <c r="N57" s="12">
         <v>3785</v>
       </c>
-      <c r="O57" s="23" t="s">
+      <c r="O57" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="P57" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q57" s="24" t="str">
+      <c r="P57" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q57" t="str">
         <f t="shared" si="1"/>
         <v>Achived</v>
       </c>
@@ -4846,56 +4920,56 @@
       </c>
     </row>
     <row r="58" spans="1:18">
-      <c r="A58" s="23" t="s">
+      <c r="A58" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="B58" s="23" t="s">
+      <c r="B58" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="C58" s="23" t="s">
+      <c r="C58" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D58" s="23" t="str">
+      <c r="D58" s="12" t="str">
         <f t="shared" si="0"/>
         <v>South</v>
       </c>
-      <c r="E58" s="23" t="s">
+      <c r="E58" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="F58" s="23" t="s">
+      <c r="F58" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G58" s="23" t="s">
+      <c r="G58" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="H58" s="23">
+      <c r="H58" s="12">
         <v>15307</v>
       </c>
-      <c r="I58" s="23">
+      <c r="I58" s="12">
         <v>18154</v>
       </c>
-      <c r="J58" s="23" t="s">
+      <c r="J58" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="K58" s="23" t="s">
+      <c r="K58" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="L58" s="23" t="s">
+      <c r="L58" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="M58" s="23">
+      <c r="M58" s="12">
         <v>2</v>
       </c>
-      <c r="N58" s="23">
+      <c r="N58" s="12">
         <v>5440</v>
       </c>
-      <c r="O58" s="23" t="s">
+      <c r="O58" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="P58" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q58" s="24" t="str">
+      <c r="P58" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q58" t="str">
         <f t="shared" si="1"/>
         <v>Not Achieved</v>
       </c>
@@ -4905,56 +4979,56 @@
       </c>
     </row>
     <row r="59" spans="1:18">
-      <c r="A59" s="23" t="s">
+      <c r="A59" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="B59" s="23" t="s">
+      <c r="B59" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="C59" s="23" t="s">
+      <c r="C59" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D59" s="23" t="str">
+      <c r="D59" s="12" t="str">
         <f t="shared" si="0"/>
         <v>South</v>
       </c>
-      <c r="E59" s="23" t="s">
+      <c r="E59" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="F59" s="23" t="s">
+      <c r="F59" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G59" s="23" t="s">
+      <c r="G59" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="H59" s="23">
+      <c r="H59" s="12">
         <v>59492</v>
       </c>
-      <c r="I59" s="23">
+      <c r="I59" s="12">
         <v>32894</v>
       </c>
-      <c r="J59" s="23" t="s">
+      <c r="J59" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="K59" s="23" t="s">
+      <c r="K59" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="L59" s="23" t="s">
+      <c r="L59" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="M59" s="23">
+      <c r="M59" s="12">
         <v>15</v>
       </c>
-      <c r="N59" s="23">
+      <c r="N59" s="12">
         <v>10702</v>
       </c>
-      <c r="O59" s="23" t="s">
+      <c r="O59" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="P59" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q59" s="24" t="str">
+      <c r="P59" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q59" t="str">
         <f t="shared" si="1"/>
         <v>Achived</v>
       </c>
@@ -4964,56 +5038,56 @@
       </c>
     </row>
     <row r="60" spans="1:18">
-      <c r="A60" s="23" t="s">
+      <c r="A60" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="B60" s="23" t="s">
+      <c r="B60" s="12" t="s">
         <v>146</v>
       </c>
-      <c r="C60" s="23" t="s">
+      <c r="C60" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="D60" s="23" t="str">
+      <c r="D60" s="12" t="str">
         <f t="shared" si="0"/>
         <v>South</v>
       </c>
-      <c r="E60" s="23" t="s">
+      <c r="E60" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="F60" s="23" t="s">
+      <c r="F60" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G60" s="23" t="s">
+      <c r="G60" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="H60" s="23">
+      <c r="H60" s="12">
         <v>35971</v>
       </c>
-      <c r="I60" s="23">
+      <c r="I60" s="12">
         <v>36490</v>
       </c>
-      <c r="J60" s="23" t="s">
+      <c r="J60" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="K60" s="23" t="s">
+      <c r="K60" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="L60" s="23" t="s">
+      <c r="L60" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="M60" s="23">
+      <c r="M60" s="12">
         <v>20</v>
       </c>
-      <c r="N60" s="23">
+      <c r="N60" s="12">
         <v>6919</v>
       </c>
-      <c r="O60" s="23" t="s">
+      <c r="O60" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="P60" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q60" s="24" t="str">
+      <c r="P60" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q60" t="str">
         <f t="shared" si="1"/>
         <v>Not Achieved</v>
       </c>
@@ -5023,56 +5097,56 @@
       </c>
     </row>
     <row r="61" spans="1:18">
-      <c r="A61" s="23" t="s">
+      <c r="A61" s="12" t="s">
         <v>147</v>
       </c>
-      <c r="B61" s="23" t="s">
+      <c r="B61" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="C61" s="23" t="s">
+      <c r="C61" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="D61" s="23" t="str">
+      <c r="D61" s="12" t="str">
         <f t="shared" si="0"/>
         <v>South</v>
       </c>
-      <c r="E61" s="23" t="s">
+      <c r="E61" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="F61" s="23" t="s">
+      <c r="F61" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="G61" s="23" t="s">
+      <c r="G61" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="H61" s="23">
+      <c r="H61" s="12">
         <v>16735</v>
       </c>
-      <c r="I61" s="23">
+      <c r="I61" s="12">
         <v>47377</v>
       </c>
-      <c r="J61" s="23" t="s">
+      <c r="J61" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="K61" s="23" t="s">
+      <c r="K61" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="L61" s="23" t="s">
+      <c r="L61" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="M61" s="23">
+      <c r="M61" s="12">
         <v>27</v>
       </c>
-      <c r="N61" s="23">
+      <c r="N61" s="12">
         <v>8866</v>
       </c>
-      <c r="O61" s="23" t="s">
+      <c r="O61" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="P61" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q61" s="24" t="str">
+      <c r="P61" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q61" t="str">
         <f t="shared" si="1"/>
         <v>Not Achieved</v>
       </c>
@@ -5082,56 +5156,56 @@
       </c>
     </row>
     <row r="62" spans="1:18">
-      <c r="A62" s="23" t="s">
+      <c r="A62" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="B62" s="23" t="s">
+      <c r="B62" s="12" t="s">
         <v>149</v>
       </c>
-      <c r="C62" s="23" t="s">
+      <c r="C62" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D62" s="23" t="str">
+      <c r="D62" s="12" t="str">
         <f t="shared" si="0"/>
         <v>South</v>
       </c>
-      <c r="E62" s="23" t="s">
+      <c r="E62" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="F62" s="23" t="s">
+      <c r="F62" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="G62" s="23" t="s">
+      <c r="G62" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="H62" s="23">
+      <c r="H62" s="12">
         <v>20272</v>
       </c>
-      <c r="I62" s="23">
+      <c r="I62" s="12">
         <v>50954</v>
       </c>
-      <c r="J62" s="23" t="s">
+      <c r="J62" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="K62" s="23" t="s">
+      <c r="K62" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="L62" s="23" t="s">
+      <c r="L62" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="M62" s="23">
+      <c r="M62" s="12">
         <v>22</v>
       </c>
-      <c r="N62" s="23">
+      <c r="N62" s="12">
         <v>2446</v>
       </c>
-      <c r="O62" s="23" t="s">
+      <c r="O62" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="P62" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q62" s="24" t="str">
+      <c r="P62" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q62" t="str">
         <f t="shared" si="1"/>
         <v>Not Achieved</v>
       </c>
@@ -5141,56 +5215,56 @@
       </c>
     </row>
     <row r="63" spans="1:18">
-      <c r="A63" s="23" t="s">
+      <c r="A63" s="12" t="s">
         <v>150</v>
       </c>
-      <c r="B63" s="23" t="s">
+      <c r="B63" s="12" t="s">
         <v>149</v>
       </c>
-      <c r="C63" s="23" t="s">
+      <c r="C63" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="D63" s="23" t="str">
+      <c r="D63" s="12" t="str">
         <f t="shared" si="0"/>
         <v>South</v>
       </c>
-      <c r="E63" s="23" t="s">
+      <c r="E63" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="F63" s="23" t="s">
+      <c r="F63" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G63" s="23" t="s">
+      <c r="G63" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="H63" s="23">
+      <c r="H63" s="12">
         <v>1300</v>
       </c>
-      <c r="I63" s="23">
+      <c r="I63" s="12">
         <v>50156</v>
       </c>
-      <c r="J63" s="23" t="s">
+      <c r="J63" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="K63" s="23" t="s">
+      <c r="K63" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="L63" s="23" t="s">
+      <c r="L63" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="M63" s="23">
+      <c r="M63" s="12">
         <v>14</v>
       </c>
-      <c r="N63" s="23">
+      <c r="N63" s="12">
         <v>7710</v>
       </c>
-      <c r="O63" s="23" t="s">
+      <c r="O63" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="P63" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q63" s="24" t="str">
+      <c r="P63" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q63" t="str">
         <f t="shared" si="1"/>
         <v>Not Achieved</v>
       </c>
@@ -5200,56 +5274,56 @@
       </c>
     </row>
     <row r="64" spans="1:18">
-      <c r="A64" s="23" t="s">
+      <c r="A64" s="12" t="s">
         <v>151</v>
       </c>
-      <c r="B64" s="23" t="s">
+      <c r="B64" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="C64" s="23" t="s">
+      <c r="C64" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D64" s="23" t="str">
+      <c r="D64" s="12" t="str">
         <f t="shared" si="0"/>
         <v>South</v>
       </c>
-      <c r="E64" s="23" t="s">
+      <c r="E64" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="F64" s="23" t="s">
+      <c r="F64" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="G64" s="23" t="s">
+      <c r="G64" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="H64" s="23">
+      <c r="H64" s="12">
         <v>2030</v>
       </c>
-      <c r="I64" s="23">
+      <c r="I64" s="12">
         <v>57433</v>
       </c>
-      <c r="J64" s="23" t="s">
+      <c r="J64" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="K64" s="23" t="s">
+      <c r="K64" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="L64" s="23" t="s">
+      <c r="L64" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="M64" s="23">
+      <c r="M64" s="12">
         <v>26</v>
       </c>
-      <c r="N64" s="23">
+      <c r="N64" s="12">
         <v>8889</v>
       </c>
-      <c r="O64" s="23" t="s">
+      <c r="O64" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="P64" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q64" s="24" t="str">
+      <c r="P64" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q64" t="str">
         <f t="shared" si="1"/>
         <v>Not Achieved</v>
       </c>
@@ -5259,56 +5333,56 @@
       </c>
     </row>
     <row r="65" spans="1:18">
-      <c r="A65" s="23" t="s">
+      <c r="A65" s="12" t="s">
         <v>152</v>
       </c>
-      <c r="B65" s="23" t="s">
+      <c r="B65" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="C65" s="23" t="s">
+      <c r="C65" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="D65" s="23" t="str">
+      <c r="D65" s="12" t="str">
         <f t="shared" si="0"/>
         <v>North</v>
       </c>
-      <c r="E65" s="23" t="s">
+      <c r="E65" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="F65" s="23" t="s">
+      <c r="F65" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G65" s="23" t="s">
+      <c r="G65" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="H65" s="23">
+      <c r="H65" s="12">
         <v>56024</v>
       </c>
-      <c r="I65" s="23">
+      <c r="I65" s="12">
         <v>49981</v>
       </c>
-      <c r="J65" s="23" t="s">
+      <c r="J65" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="K65" s="23" t="s">
+      <c r="K65" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="L65" s="23" t="s">
+      <c r="L65" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="M65" s="23">
+      <c r="M65" s="12">
         <v>20</v>
       </c>
-      <c r="N65" s="23">
+      <c r="N65" s="12">
         <v>13552</v>
       </c>
-      <c r="O65" s="23" t="s">
+      <c r="O65" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="P65" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q65" s="24" t="str">
+      <c r="P65" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q65" t="str">
         <f t="shared" si="1"/>
         <v>Achived</v>
       </c>
@@ -5318,56 +5392,56 @@
       </c>
     </row>
     <row r="66" spans="1:18">
-      <c r="A66" s="23" t="s">
+      <c r="A66" s="12" t="s">
         <v>153</v>
       </c>
-      <c r="B66" s="23" t="s">
+      <c r="B66" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="C66" s="23" t="s">
+      <c r="C66" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="D66" s="23" t="str">
+      <c r="D66" s="12" t="str">
         <f t="shared" si="0"/>
         <v>East</v>
       </c>
-      <c r="E66" s="23" t="s">
+      <c r="E66" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="F66" s="23" t="s">
+      <c r="F66" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="G66" s="23" t="s">
+      <c r="G66" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="H66" s="23">
+      <c r="H66" s="12">
         <v>46447</v>
       </c>
-      <c r="I66" s="23">
+      <c r="I66" s="12">
         <v>50530</v>
       </c>
-      <c r="J66" s="23" t="s">
+      <c r="J66" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="K66" s="23" t="s">
+      <c r="K66" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="L66" s="23" t="s">
+      <c r="L66" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="M66" s="23">
+      <c r="M66" s="12">
         <v>25</v>
       </c>
-      <c r="N66" s="23">
+      <c r="N66" s="12">
         <v>3586</v>
       </c>
-      <c r="O66" s="23" t="s">
+      <c r="O66" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="P66" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q66" s="24" t="str">
+      <c r="P66" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q66" t="str">
         <f t="shared" si="1"/>
         <v>Not Achieved</v>
       </c>
@@ -5377,56 +5451,56 @@
       </c>
     </row>
     <row r="67" spans="1:18">
-      <c r="A67" s="23" t="s">
+      <c r="A67" s="12" t="s">
         <v>154</v>
       </c>
-      <c r="B67" s="23" t="s">
+      <c r="B67" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="C67" s="23" t="s">
+      <c r="C67" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D67" s="23" t="str">
+      <c r="D67" s="12" t="str">
         <f t="shared" si="0"/>
         <v>South</v>
       </c>
-      <c r="E67" s="23" t="s">
+      <c r="E67" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="F67" s="23" t="s">
+      <c r="F67" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="G67" s="23" t="s">
+      <c r="G67" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="H67" s="23">
+      <c r="H67" s="12">
         <v>61107</v>
       </c>
-      <c r="I67" s="23">
+      <c r="I67" s="12">
         <v>27563</v>
       </c>
-      <c r="J67" s="23" t="s">
+      <c r="J67" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="K67" s="23" t="s">
+      <c r="K67" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="L67" s="23" t="s">
+      <c r="L67" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="M67" s="23">
+      <c r="M67" s="12">
         <v>14</v>
       </c>
-      <c r="N67" s="23">
+      <c r="N67" s="12">
         <v>16961</v>
       </c>
-      <c r="O67" s="23" t="s">
+      <c r="O67" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="P67" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q67" s="24" t="str">
+      <c r="P67" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q67" t="str">
         <f t="shared" si="1"/>
         <v>Achived</v>
       </c>
@@ -5436,56 +5510,56 @@
       </c>
     </row>
     <row r="68" spans="1:18">
-      <c r="A68" s="23" t="s">
+      <c r="A68" s="12" t="s">
         <v>155</v>
       </c>
-      <c r="B68" s="23" t="s">
+      <c r="B68" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="C68" s="23" t="s">
+      <c r="C68" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D68" s="23" t="str">
+      <c r="D68" s="12" t="str">
         <f t="shared" ref="D68:D102" si="3">PROPER(TRIM(C68))</f>
         <v>South</v>
       </c>
-      <c r="E68" s="23" t="s">
+      <c r="E68" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="F68" s="23" t="s">
+      <c r="F68" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G68" s="23" t="s">
+      <c r="G68" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="H68" s="23">
+      <c r="H68" s="12">
         <v>39030</v>
       </c>
-      <c r="I68" s="23">
+      <c r="I68" s="12">
         <v>21658</v>
       </c>
-      <c r="J68" s="23" t="s">
+      <c r="J68" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="K68" s="23" t="s">
+      <c r="K68" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="L68" s="23" t="s">
+      <c r="L68" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="M68" s="23">
+      <c r="M68" s="12">
         <v>24</v>
       </c>
-      <c r="N68" s="23">
+      <c r="N68" s="12">
         <v>4530</v>
       </c>
-      <c r="O68" s="23" t="s">
+      <c r="O68" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="P68" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q68" s="24" t="str">
+      <c r="P68" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q68" t="str">
         <f t="shared" ref="Q68:Q102" si="4">IF(H68&gt;I68,"Achived","Not Achieved")</f>
         <v>Achived</v>
       </c>
@@ -5495,56 +5569,56 @@
       </c>
     </row>
     <row r="69" spans="1:18">
-      <c r="A69" s="23" t="s">
+      <c r="A69" s="12" t="s">
         <v>156</v>
       </c>
-      <c r="B69" s="23" t="s">
+      <c r="B69" s="12" t="s">
         <v>157</v>
       </c>
-      <c r="C69" s="23" t="s">
+      <c r="C69" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="D69" s="23" t="str">
+      <c r="D69" s="12" t="str">
         <f t="shared" si="3"/>
         <v>South</v>
       </c>
-      <c r="E69" s="23" t="s">
+      <c r="E69" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="F69" s="23" t="s">
+      <c r="F69" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G69" s="23" t="s">
+      <c r="G69" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="H69" s="23">
+      <c r="H69" s="12">
         <v>56878</v>
       </c>
-      <c r="I69" s="23">
+      <c r="I69" s="12">
         <v>25103</v>
       </c>
-      <c r="J69" s="23" t="s">
+      <c r="J69" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="K69" s="23" t="s">
+      <c r="K69" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="L69" s="23" t="s">
+      <c r="L69" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="M69" s="23">
+      <c r="M69" s="12">
         <v>18</v>
       </c>
-      <c r="N69" s="23">
+      <c r="N69" s="12">
         <v>15227</v>
       </c>
-      <c r="O69" s="23" t="s">
+      <c r="O69" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="P69" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q69" s="24" t="str">
+      <c r="P69" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q69" t="str">
         <f t="shared" si="4"/>
         <v>Achived</v>
       </c>
@@ -5554,56 +5628,56 @@
       </c>
     </row>
     <row r="70" spans="1:18">
-      <c r="A70" s="23" t="s">
+      <c r="A70" s="12" t="s">
         <v>158</v>
       </c>
-      <c r="B70" s="23" t="s">
+      <c r="B70" s="12" t="s">
         <v>159</v>
       </c>
-      <c r="C70" s="23" t="s">
+      <c r="C70" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="D70" s="23" t="str">
+      <c r="D70" s="12" t="str">
         <f t="shared" si="3"/>
         <v>South</v>
       </c>
-      <c r="E70" s="23" t="s">
+      <c r="E70" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="F70" s="23" t="s">
+      <c r="F70" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G70" s="23" t="s">
+      <c r="G70" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="H70" s="23">
+      <c r="H70" s="12">
         <v>23236</v>
       </c>
-      <c r="I70" s="23">
+      <c r="I70" s="12">
         <v>39566</v>
       </c>
-      <c r="J70" s="23" t="s">
+      <c r="J70" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="K70" s="23" t="s">
+      <c r="K70" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="L70" s="23" t="s">
+      <c r="L70" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="M70" s="23">
+      <c r="M70" s="12">
         <v>7</v>
       </c>
-      <c r="N70" s="23">
+      <c r="N70" s="12">
         <v>10315</v>
       </c>
-      <c r="O70" s="23" t="s">
+      <c r="O70" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="P70" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q70" s="24" t="str">
+      <c r="P70" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q70" t="str">
         <f t="shared" si="4"/>
         <v>Not Achieved</v>
       </c>
@@ -5613,56 +5687,56 @@
       </c>
     </row>
     <row r="71" spans="1:18">
-      <c r="A71" s="23" t="s">
+      <c r="A71" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="B71" s="23" t="s">
+      <c r="B71" s="12" t="s">
         <v>161</v>
       </c>
-      <c r="C71" s="23" t="s">
+      <c r="C71" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="D71" s="23" t="str">
+      <c r="D71" s="12" t="str">
         <f t="shared" si="3"/>
         <v>North</v>
       </c>
-      <c r="E71" s="23" t="s">
+      <c r="E71" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="F71" s="23" t="s">
+      <c r="F71" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G71" s="23" t="s">
+      <c r="G71" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="H71" s="23">
+      <c r="H71" s="12">
         <v>39136</v>
       </c>
-      <c r="I71" s="23">
+      <c r="I71" s="12">
         <v>19859</v>
       </c>
-      <c r="J71" s="23" t="s">
+      <c r="J71" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="K71" s="23" t="s">
+      <c r="K71" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="L71" s="23" t="s">
+      <c r="L71" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="M71" s="23">
+      <c r="M71" s="12">
         <v>24</v>
       </c>
-      <c r="N71" s="23">
+      <c r="N71" s="12">
         <v>10628</v>
       </c>
-      <c r="O71" s="23" t="s">
+      <c r="O71" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="P71" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q71" s="24" t="str">
+      <c r="P71" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q71" t="str">
         <f t="shared" si="4"/>
         <v>Achived</v>
       </c>
@@ -5672,56 +5746,56 @@
       </c>
     </row>
     <row r="72" spans="1:18">
-      <c r="A72" s="23" t="s">
+      <c r="A72" s="12" t="s">
         <v>162</v>
       </c>
-      <c r="B72" s="23" t="s">
+      <c r="B72" s="12" t="s">
         <v>163</v>
       </c>
-      <c r="C72" s="23" t="s">
+      <c r="C72" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="D72" s="23" t="str">
+      <c r="D72" s="12" t="str">
         <f t="shared" si="3"/>
         <v>South</v>
       </c>
-      <c r="E72" s="23" t="s">
+      <c r="E72" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="F72" s="23" t="s">
+      <c r="F72" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G72" s="23" t="s">
+      <c r="G72" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="H72" s="23">
+      <c r="H72" s="12">
         <v>11817</v>
       </c>
-      <c r="I72" s="23">
+      <c r="I72" s="12">
         <v>34597</v>
       </c>
-      <c r="J72" s="23" t="s">
+      <c r="J72" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="K72" s="23" t="s">
+      <c r="K72" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="L72" s="23" t="s">
+      <c r="L72" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="M72" s="23">
+      <c r="M72" s="12">
         <v>22</v>
       </c>
-      <c r="N72" s="23">
+      <c r="N72" s="12">
         <v>1843</v>
       </c>
-      <c r="O72" s="23" t="s">
+      <c r="O72" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="P72" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q72" s="24" t="str">
+      <c r="P72" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q72" t="str">
         <f t="shared" si="4"/>
         <v>Not Achieved</v>
       </c>
@@ -5731,56 +5805,56 @@
       </c>
     </row>
     <row r="73" spans="1:18">
-      <c r="A73" s="23" t="s">
+      <c r="A73" s="12" t="s">
         <v>164</v>
       </c>
-      <c r="B73" s="23" t="s">
+      <c r="B73" s="12" t="s">
         <v>165</v>
       </c>
-      <c r="C73" s="23" t="s">
+      <c r="C73" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="D73" s="23" t="str">
+      <c r="D73" s="12" t="str">
         <f t="shared" si="3"/>
         <v>West</v>
       </c>
-      <c r="E73" s="23" t="s">
+      <c r="E73" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="F73" s="23" t="s">
+      <c r="F73" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="G73" s="23" t="s">
+      <c r="G73" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="H73" s="23">
+      <c r="H73" s="12">
         <v>11639</v>
       </c>
-      <c r="I73" s="23">
+      <c r="I73" s="12">
         <v>35474</v>
       </c>
-      <c r="J73" s="23" t="s">
+      <c r="J73" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="K73" s="23" t="s">
+      <c r="K73" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="L73" s="23" t="s">
+      <c r="L73" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="M73" s="23">
+      <c r="M73" s="12">
         <v>5</v>
       </c>
-      <c r="N73" s="23">
+      <c r="N73" s="12">
         <v>10241</v>
       </c>
-      <c r="O73" s="23" t="s">
+      <c r="O73" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="P73" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q73" s="24" t="str">
+      <c r="P73" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q73" t="str">
         <f t="shared" si="4"/>
         <v>Not Achieved</v>
       </c>
@@ -5790,56 +5864,56 @@
       </c>
     </row>
     <row r="74" spans="1:18">
-      <c r="A74" s="23" t="s">
+      <c r="A74" s="12" t="s">
         <v>166</v>
       </c>
-      <c r="B74" s="23" t="s">
+      <c r="B74" s="12" t="s">
         <v>167</v>
       </c>
-      <c r="C74" s="23" t="s">
+      <c r="C74" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="D74" s="23" t="str">
+      <c r="D74" s="12" t="str">
         <f t="shared" si="3"/>
         <v>West</v>
       </c>
-      <c r="E74" s="23" t="s">
+      <c r="E74" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="F74" s="23" t="s">
+      <c r="F74" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G74" s="23" t="s">
+      <c r="G74" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="H74" s="23">
+      <c r="H74" s="12">
         <v>296</v>
       </c>
-      <c r="I74" s="23">
+      <c r="I74" s="12">
         <v>51456</v>
       </c>
-      <c r="J74" s="23" t="s">
+      <c r="J74" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="K74" s="23" t="s">
+      <c r="K74" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="L74" s="23" t="s">
+      <c r="L74" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="M74" s="23">
+      <c r="M74" s="12">
         <v>4</v>
       </c>
-      <c r="N74" s="23">
+      <c r="N74" s="12">
         <v>39</v>
       </c>
-      <c r="O74" s="23" t="s">
+      <c r="O74" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="P74" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q74" s="24" t="str">
+      <c r="P74" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q74" t="str">
         <f t="shared" si="4"/>
         <v>Not Achieved</v>
       </c>
@@ -5849,56 +5923,56 @@
       </c>
     </row>
     <row r="75" spans="1:18">
-      <c r="A75" s="23" t="s">
+      <c r="A75" s="12" t="s">
         <v>168</v>
       </c>
-      <c r="B75" s="23" t="s">
+      <c r="B75" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="C75" s="23" t="s">
+      <c r="C75" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D75" s="23" t="str">
+      <c r="D75" s="12" t="str">
         <f t="shared" si="3"/>
         <v>South</v>
       </c>
-      <c r="E75" s="23" t="s">
+      <c r="E75" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="F75" s="23" t="s">
+      <c r="F75" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G75" s="23" t="s">
+      <c r="G75" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="H75" s="23">
+      <c r="H75" s="12">
         <v>48915</v>
       </c>
-      <c r="I75" s="23">
+      <c r="I75" s="12">
         <v>33243</v>
       </c>
-      <c r="J75" s="23" t="s">
+      <c r="J75" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="K75" s="23" t="s">
+      <c r="K75" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="L75" s="23" t="s">
+      <c r="L75" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="M75" s="23">
+      <c r="M75" s="12">
         <v>22</v>
       </c>
-      <c r="N75" s="23">
+      <c r="N75" s="12">
         <v>5162</v>
       </c>
-      <c r="O75" s="23" t="s">
+      <c r="O75" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="P75" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q75" s="24" t="str">
+      <c r="P75" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q75" t="str">
         <f t="shared" si="4"/>
         <v>Achived</v>
       </c>
@@ -5908,56 +5982,56 @@
       </c>
     </row>
     <row r="76" spans="1:18">
-      <c r="A76" s="23" t="s">
+      <c r="A76" s="12" t="s">
         <v>169</v>
       </c>
-      <c r="B76" s="23" t="s">
+      <c r="B76" s="12" t="s">
         <v>170</v>
       </c>
-      <c r="C76" s="23" t="s">
+      <c r="C76" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D76" s="23" t="str">
+      <c r="D76" s="12" t="str">
         <f t="shared" si="3"/>
         <v>South</v>
       </c>
-      <c r="E76" s="23" t="s">
+      <c r="E76" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="F76" s="23" t="s">
+      <c r="F76" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G76" s="23" t="s">
+      <c r="G76" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="H76" s="23">
+      <c r="H76" s="12">
         <v>15740</v>
       </c>
-      <c r="I76" s="23">
+      <c r="I76" s="12">
         <v>24862</v>
       </c>
-      <c r="J76" s="23" t="s">
+      <c r="J76" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="K76" s="23" t="s">
+      <c r="K76" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="L76" s="23" t="s">
+      <c r="L76" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="M76" s="23">
+      <c r="M76" s="12">
         <v>10</v>
       </c>
-      <c r="N76" s="23">
+      <c r="N76" s="12">
         <v>15718</v>
       </c>
-      <c r="O76" s="23" t="s">
+      <c r="O76" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="P76" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q76" s="24" t="str">
+      <c r="P76" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q76" t="str">
         <f t="shared" si="4"/>
         <v>Not Achieved</v>
       </c>
@@ -5967,56 +6041,56 @@
       </c>
     </row>
     <row r="77" spans="1:18">
-      <c r="A77" s="23" t="s">
+      <c r="A77" s="12" t="s">
         <v>171</v>
       </c>
-      <c r="B77" s="23" t="s">
+      <c r="B77" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="C77" s="23" t="s">
+      <c r="C77" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="D77" s="23" t="str">
+      <c r="D77" s="12" t="str">
         <f t="shared" si="3"/>
         <v>East</v>
       </c>
-      <c r="E77" s="23" t="s">
+      <c r="E77" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="F77" s="23" t="s">
+      <c r="F77" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="G77" s="23" t="s">
+      <c r="G77" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="H77" s="23">
+      <c r="H77" s="12">
         <v>45941</v>
       </c>
-      <c r="I77" s="23">
+      <c r="I77" s="12">
         <v>39851</v>
       </c>
-      <c r="J77" s="23" t="s">
+      <c r="J77" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="K77" s="23" t="s">
+      <c r="K77" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="L77" s="23" t="s">
+      <c r="L77" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="M77" s="23">
+      <c r="M77" s="12">
         <v>21</v>
       </c>
-      <c r="N77" s="23">
+      <c r="N77" s="12">
         <v>3092</v>
       </c>
-      <c r="O77" s="23" t="s">
+      <c r="O77" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="P77" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q77" s="24" t="str">
+      <c r="P77" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q77" t="str">
         <f t="shared" si="4"/>
         <v>Achived</v>
       </c>
@@ -6026,56 +6100,56 @@
       </c>
     </row>
     <row r="78" spans="1:18">
-      <c r="A78" s="23" t="s">
+      <c r="A78" s="12" t="s">
         <v>172</v>
       </c>
-      <c r="B78" s="23" t="s">
+      <c r="B78" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="C78" s="23" t="s">
+      <c r="C78" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D78" s="23" t="str">
+      <c r="D78" s="12" t="str">
         <f t="shared" si="3"/>
         <v>South</v>
       </c>
-      <c r="E78" s="23" t="s">
+      <c r="E78" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="F78" s="23" t="s">
+      <c r="F78" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="G78" s="23" t="s">
+      <c r="G78" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="H78" s="23">
+      <c r="H78" s="12">
         <v>56548</v>
       </c>
-      <c r="I78" s="23">
+      <c r="I78" s="12">
         <v>13173</v>
       </c>
-      <c r="J78" s="23" t="s">
+      <c r="J78" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="K78" s="23" t="s">
+      <c r="K78" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="L78" s="23" t="s">
+      <c r="L78" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="M78" s="23">
+      <c r="M78" s="12">
         <v>8</v>
       </c>
-      <c r="N78" s="23">
+      <c r="N78" s="12">
         <v>2802</v>
       </c>
-      <c r="O78" s="23" t="s">
+      <c r="O78" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="P78" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q78" s="24" t="str">
+      <c r="P78" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q78" t="str">
         <f t="shared" si="4"/>
         <v>Achived</v>
       </c>
@@ -6085,56 +6159,56 @@
       </c>
     </row>
     <row r="79" spans="1:18">
-      <c r="A79" s="23" t="s">
+      <c r="A79" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="B79" s="23" t="s">
+      <c r="B79" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="C79" s="23" t="s">
+      <c r="C79" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="D79" s="23" t="str">
+      <c r="D79" s="12" t="str">
         <f t="shared" si="3"/>
         <v>South</v>
       </c>
-      <c r="E79" s="23" t="s">
+      <c r="E79" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="F79" s="23" t="s">
+      <c r="F79" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G79" s="23" t="s">
+      <c r="G79" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="H79" s="23">
+      <c r="H79" s="12">
         <v>555</v>
       </c>
-      <c r="I79" s="23">
+      <c r="I79" s="12">
         <v>31401</v>
       </c>
-      <c r="J79" s="23" t="s">
+      <c r="J79" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="K79" s="23" t="s">
+      <c r="K79" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="L79" s="23" t="s">
+      <c r="L79" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="M79" s="23">
+      <c r="M79" s="12">
         <v>10</v>
       </c>
-      <c r="N79" s="23">
+      <c r="N79" s="12">
         <v>-1870</v>
       </c>
-      <c r="O79" s="23" t="s">
+      <c r="O79" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="P79" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q79" s="24" t="str">
+      <c r="P79" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q79" t="str">
         <f t="shared" si="4"/>
         <v>Not Achieved</v>
       </c>
@@ -6144,56 +6218,56 @@
       </c>
     </row>
     <row r="80" spans="1:18">
-      <c r="A80" s="23" t="s">
+      <c r="A80" s="12" t="s">
         <v>174</v>
       </c>
-      <c r="B80" s="23" t="s">
+      <c r="B80" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="C80" s="23" t="s">
+      <c r="C80" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="D80" s="23" t="str">
+      <c r="D80" s="12" t="str">
         <f t="shared" si="3"/>
         <v>South</v>
       </c>
-      <c r="E80" s="23" t="s">
+      <c r="E80" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="F80" s="23" t="s">
+      <c r="F80" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G80" s="23" t="s">
+      <c r="G80" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="H80" s="23">
+      <c r="H80" s="12">
         <v>23547</v>
       </c>
-      <c r="I80" s="23">
+      <c r="I80" s="12">
         <v>56701</v>
       </c>
-      <c r="J80" s="23" t="s">
+      <c r="J80" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="K80" s="23" t="s">
+      <c r="K80" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="L80" s="23" t="s">
+      <c r="L80" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="M80" s="23">
+      <c r="M80" s="12">
         <v>16</v>
       </c>
-      <c r="N80" s="23">
+      <c r="N80" s="12">
         <v>19687</v>
       </c>
-      <c r="O80" s="23" t="s">
+      <c r="O80" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="P80" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q80" s="24" t="str">
+      <c r="P80" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q80" t="str">
         <f t="shared" si="4"/>
         <v>Not Achieved</v>
       </c>
@@ -6203,56 +6277,56 @@
       </c>
     </row>
     <row r="81" spans="1:18">
-      <c r="A81" s="23" t="s">
+      <c r="A81" s="12" t="s">
         <v>175</v>
       </c>
-      <c r="B81" s="23" t="s">
+      <c r="B81" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="C81" s="23" t="s">
+      <c r="C81" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="D81" s="23" t="str">
+      <c r="D81" s="12" t="str">
         <f t="shared" si="3"/>
         <v>North</v>
       </c>
-      <c r="E81" s="23" t="s">
+      <c r="E81" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="F81" s="23" t="s">
+      <c r="F81" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G81" s="23" t="s">
+      <c r="G81" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="H81" s="23">
+      <c r="H81" s="12">
         <v>13875</v>
       </c>
-      <c r="I81" s="23">
+      <c r="I81" s="12">
         <v>30303</v>
       </c>
-      <c r="J81" s="23" t="s">
+      <c r="J81" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="K81" s="23" t="s">
+      <c r="K81" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="L81" s="23" t="s">
+      <c r="L81" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="M81" s="23">
+      <c r="M81" s="12">
         <v>29</v>
       </c>
-      <c r="N81" s="23">
+      <c r="N81" s="12">
         <v>17281</v>
       </c>
-      <c r="O81" s="23" t="s">
+      <c r="O81" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="P81" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q81" s="24" t="str">
+      <c r="P81" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q81" t="str">
         <f t="shared" si="4"/>
         <v>Not Achieved</v>
       </c>
@@ -6262,56 +6336,56 @@
       </c>
     </row>
     <row r="82" spans="1:18">
-      <c r="A82" s="23" t="s">
+      <c r="A82" s="12" t="s">
         <v>176</v>
       </c>
-      <c r="B82" s="23" t="s">
+      <c r="B82" s="12" t="s">
         <v>170</v>
       </c>
-      <c r="C82" s="23" t="s">
+      <c r="C82" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D82" s="23" t="str">
+      <c r="D82" s="12" t="str">
         <f t="shared" si="3"/>
         <v>South</v>
       </c>
-      <c r="E82" s="23" t="s">
+      <c r="E82" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="F82" s="23" t="s">
+      <c r="F82" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="G82" s="23" t="s">
+      <c r="G82" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="H82" s="23">
+      <c r="H82" s="12">
         <v>61063</v>
       </c>
-      <c r="I82" s="23">
+      <c r="I82" s="12">
         <v>58900</v>
       </c>
-      <c r="J82" s="23" t="s">
+      <c r="J82" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="K82" s="23" t="s">
+      <c r="K82" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="L82" s="23" t="s">
+      <c r="L82" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="M82" s="23">
+      <c r="M82" s="12">
         <v>0</v>
       </c>
-      <c r="N82" s="23">
+      <c r="N82" s="12">
         <v>10636</v>
       </c>
-      <c r="O82" s="23" t="s">
+      <c r="O82" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="P82" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q82" s="24" t="str">
+      <c r="P82" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q82" t="str">
         <f t="shared" si="4"/>
         <v>Achived</v>
       </c>
@@ -6321,56 +6395,56 @@
       </c>
     </row>
     <row r="83" spans="1:18">
-      <c r="A83" s="23" t="s">
+      <c r="A83" s="12" t="s">
         <v>177</v>
       </c>
-      <c r="B83" s="23" t="s">
+      <c r="B83" s="12" t="s">
         <v>178</v>
       </c>
-      <c r="C83" s="23" t="s">
+      <c r="C83" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="D83" s="23" t="str">
+      <c r="D83" s="12" t="str">
         <f t="shared" si="3"/>
         <v>North</v>
       </c>
-      <c r="E83" s="23" t="s">
+      <c r="E83" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="F83" s="23" t="s">
+      <c r="F83" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G83" s="23" t="s">
+      <c r="G83" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="H83" s="23">
+      <c r="H83" s="12">
         <v>39853</v>
       </c>
-      <c r="I83" s="23">
+      <c r="I83" s="12">
         <v>38266</v>
       </c>
-      <c r="J83" s="23" t="s">
+      <c r="J83" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="K83" s="23" t="s">
+      <c r="K83" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="L83" s="23" t="s">
+      <c r="L83" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="M83" s="23">
+      <c r="M83" s="12">
         <v>19</v>
       </c>
-      <c r="N83" s="23">
+      <c r="N83" s="12">
         <v>-1004</v>
       </c>
-      <c r="O83" s="23" t="s">
+      <c r="O83" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="P83" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q83" s="24" t="str">
+      <c r="P83" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q83" t="str">
         <f t="shared" si="4"/>
         <v>Achived</v>
       </c>
@@ -6380,56 +6454,56 @@
       </c>
     </row>
     <row r="84" spans="1:18">
-      <c r="A84" s="23" t="s">
+      <c r="A84" s="12" t="s">
         <v>179</v>
       </c>
-      <c r="B84" s="23" t="s">
+      <c r="B84" s="12" t="s">
         <v>180</v>
       </c>
-      <c r="C84" s="23" t="s">
+      <c r="C84" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="D84" s="23" t="str">
+      <c r="D84" s="12" t="str">
         <f t="shared" si="3"/>
         <v>West</v>
       </c>
-      <c r="E84" s="23" t="s">
+      <c r="E84" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="F84" s="23" t="s">
+      <c r="F84" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G84" s="23" t="s">
+      <c r="G84" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="H84" s="23">
+      <c r="H84" s="12">
         <v>39665</v>
       </c>
-      <c r="I84" s="23">
+      <c r="I84" s="12">
         <v>45011</v>
       </c>
-      <c r="J84" s="23" t="s">
+      <c r="J84" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="K84" s="23" t="s">
+      <c r="K84" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="L84" s="23" t="s">
+      <c r="L84" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="M84" s="23">
+      <c r="M84" s="12">
         <v>29</v>
       </c>
-      <c r="N84" s="23">
+      <c r="N84" s="12">
         <v>17800</v>
       </c>
-      <c r="O84" s="23" t="s">
+      <c r="O84" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="P84" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q84" s="24" t="str">
+      <c r="P84" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q84" t="str">
         <f t="shared" si="4"/>
         <v>Not Achieved</v>
       </c>
@@ -6439,56 +6513,56 @@
       </c>
     </row>
     <row r="85" spans="1:18">
-      <c r="A85" s="23" t="s">
+      <c r="A85" s="12" t="s">
         <v>181</v>
       </c>
-      <c r="B85" s="23" t="s">
+      <c r="B85" s="12" t="s">
         <v>182</v>
       </c>
-      <c r="C85" s="23" t="s">
+      <c r="C85" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="D85" s="23" t="str">
+      <c r="D85" s="12" t="str">
         <f t="shared" si="3"/>
         <v>North</v>
       </c>
-      <c r="E85" s="23" t="s">
+      <c r="E85" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="F85" s="23" t="s">
+      <c r="F85" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="G85" s="23" t="s">
+      <c r="G85" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="H85" s="23">
+      <c r="H85" s="12">
         <v>27815</v>
       </c>
-      <c r="I85" s="23">
+      <c r="I85" s="12">
         <v>53489</v>
       </c>
-      <c r="J85" s="23" t="s">
+      <c r="J85" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="K85" s="23" t="s">
+      <c r="K85" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="L85" s="23" t="s">
+      <c r="L85" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="M85" s="23">
+      <c r="M85" s="12">
         <v>19</v>
       </c>
-      <c r="N85" s="23">
+      <c r="N85" s="12">
         <v>19088</v>
       </c>
-      <c r="O85" s="23" t="s">
+      <c r="O85" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="P85" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q85" s="24" t="str">
+      <c r="P85" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q85" t="str">
         <f t="shared" si="4"/>
         <v>Not Achieved</v>
       </c>
@@ -6498,56 +6572,56 @@
       </c>
     </row>
     <row r="86" spans="1:18">
-      <c r="A86" s="23" t="s">
+      <c r="A86" s="12" t="s">
         <v>183</v>
       </c>
-      <c r="B86" s="23" t="s">
+      <c r="B86" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="C86" s="23" t="s">
+      <c r="C86" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D86" s="23" t="str">
+      <c r="D86" s="12" t="str">
         <f t="shared" si="3"/>
         <v>South</v>
       </c>
-      <c r="E86" s="23" t="s">
+      <c r="E86" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="F86" s="23" t="s">
+      <c r="F86" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G86" s="23" t="s">
+      <c r="G86" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="H86" s="23">
+      <c r="H86" s="12">
         <v>48441</v>
       </c>
-      <c r="I86" s="23">
+      <c r="I86" s="12">
         <v>35921</v>
       </c>
-      <c r="J86" s="23" t="s">
+      <c r="J86" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="K86" s="23" t="s">
+      <c r="K86" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="L86" s="23" t="s">
+      <c r="L86" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="M86" s="23">
+      <c r="M86" s="12">
         <v>27</v>
       </c>
-      <c r="N86" s="23">
+      <c r="N86" s="12">
         <v>1705</v>
       </c>
-      <c r="O86" s="23" t="s">
+      <c r="O86" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="P86" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q86" s="24" t="str">
+      <c r="P86" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q86" t="str">
         <f t="shared" si="4"/>
         <v>Achived</v>
       </c>
@@ -6557,56 +6631,56 @@
       </c>
     </row>
     <row r="87" spans="1:18">
-      <c r="A87" s="23" t="s">
+      <c r="A87" s="12" t="s">
         <v>184</v>
       </c>
-      <c r="B87" s="23" t="s">
+      <c r="B87" s="12" t="s">
         <v>185</v>
       </c>
-      <c r="C87" s="23" t="s">
+      <c r="C87" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="D87" s="23" t="str">
+      <c r="D87" s="12" t="str">
         <f t="shared" si="3"/>
         <v>South</v>
       </c>
-      <c r="E87" s="23" t="s">
+      <c r="E87" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="F87" s="23" t="s">
+      <c r="F87" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="G87" s="23" t="s">
+      <c r="G87" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="H87" s="23">
+      <c r="H87" s="12">
         <v>43130</v>
       </c>
-      <c r="I87" s="23">
+      <c r="I87" s="12">
         <v>35309</v>
       </c>
-      <c r="J87" s="23" t="s">
+      <c r="J87" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="K87" s="23" t="s">
+      <c r="K87" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="L87" s="23" t="s">
+      <c r="L87" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="M87" s="23">
+      <c r="M87" s="12">
         <v>17</v>
       </c>
-      <c r="N87" s="23">
+      <c r="N87" s="12">
         <v>5909</v>
       </c>
-      <c r="O87" s="23" t="s">
+      <c r="O87" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="P87" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q87" s="24" t="str">
+      <c r="P87" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q87" t="str">
         <f t="shared" si="4"/>
         <v>Achived</v>
       </c>
@@ -6616,56 +6690,56 @@
       </c>
     </row>
     <row r="88" spans="1:18">
-      <c r="A88" s="23" t="s">
+      <c r="A88" s="12" t="s">
         <v>186</v>
       </c>
-      <c r="B88" s="23" t="s">
+      <c r="B88" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="C88" s="23" t="s">
+      <c r="C88" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="D88" s="23" t="str">
+      <c r="D88" s="12" t="str">
         <f t="shared" si="3"/>
         <v>South</v>
       </c>
-      <c r="E88" s="23" t="s">
+      <c r="E88" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="F88" s="23" t="s">
+      <c r="F88" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G88" s="23" t="s">
+      <c r="G88" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="H88" s="23">
+      <c r="H88" s="12">
         <v>67257</v>
       </c>
-      <c r="I88" s="23">
+      <c r="I88" s="12">
         <v>26949</v>
       </c>
-      <c r="J88" s="23" t="s">
+      <c r="J88" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="K88" s="23" t="s">
+      <c r="K88" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="L88" s="23" t="s">
+      <c r="L88" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="M88" s="23">
+      <c r="M88" s="12">
         <v>20</v>
       </c>
-      <c r="N88" s="23">
+      <c r="N88" s="12">
         <v>1078</v>
       </c>
-      <c r="O88" s="23" t="s">
+      <c r="O88" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="P88" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q88" s="24" t="str">
+      <c r="P88" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q88" t="str">
         <f t="shared" si="4"/>
         <v>Achived</v>
       </c>
@@ -6675,56 +6749,56 @@
       </c>
     </row>
     <row r="89" spans="1:18">
-      <c r="A89" s="23" t="s">
+      <c r="A89" s="12" t="s">
         <v>187</v>
       </c>
-      <c r="B89" s="23" t="s">
+      <c r="B89" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="C89" s="23" t="s">
+      <c r="C89" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="D89" s="23" t="str">
+      <c r="D89" s="12" t="str">
         <f t="shared" si="3"/>
         <v>West</v>
       </c>
-      <c r="E89" s="23" t="s">
+      <c r="E89" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="F89" s="23" t="s">
+      <c r="F89" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="G89" s="23" t="s">
+      <c r="G89" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="H89" s="23">
+      <c r="H89" s="12">
         <v>55871</v>
       </c>
-      <c r="I89" s="23">
+      <c r="I89" s="12">
         <v>19547</v>
       </c>
-      <c r="J89" s="23" t="s">
+      <c r="J89" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="K89" s="23" t="s">
+      <c r="K89" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="L89" s="23" t="s">
+      <c r="L89" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="M89" s="23">
+      <c r="M89" s="12">
         <v>6</v>
       </c>
-      <c r="N89" s="23">
+      <c r="N89" s="12">
         <v>17314</v>
       </c>
-      <c r="O89" s="23" t="s">
+      <c r="O89" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="P89" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q89" s="24" t="str">
+      <c r="P89" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q89" t="str">
         <f t="shared" si="4"/>
         <v>Achived</v>
       </c>
@@ -6734,54 +6808,54 @@
       </c>
     </row>
     <row r="90" spans="1:18">
-      <c r="A90" s="23" t="s">
+      <c r="A90" s="12" t="s">
         <v>188</v>
       </c>
-      <c r="B90" s="23" t="s">
+      <c r="B90" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="C90" s="23" t="s">
+      <c r="C90" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="D90" s="23" t="str">
+      <c r="D90" s="12" t="str">
         <f t="shared" si="3"/>
         <v>North</v>
       </c>
-      <c r="E90" s="23" t="s">
+      <c r="E90" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="F90" s="23" t="s">
+      <c r="F90" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G90" s="23" t="s">
+      <c r="G90" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="H90" s="23">
+      <c r="H90" s="12">
         <v>65324</v>
       </c>
-      <c r="I90" s="23">
+      <c r="I90" s="12">
         <v>39586</v>
       </c>
-      <c r="J90" s="23" t="s">
+      <c r="J90" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="K90" s="23" t="s">
+      <c r="K90" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="L90" s="23" t="s">
+      <c r="L90" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="M90" s="23">
+      <c r="M90" s="12">
         <v>13</v>
       </c>
-      <c r="N90" s="23">
+      <c r="N90" s="12">
         <v>3</v>
       </c>
-      <c r="O90" s="23" t="s">
+      <c r="O90" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="P90" s="23"/>
-      <c r="Q90" s="24" t="str">
+      <c r="P90" s="12"/>
+      <c r="Q90" t="str">
         <f t="shared" si="4"/>
         <v>Achived</v>
       </c>
@@ -6791,56 +6865,56 @@
       </c>
     </row>
     <row r="91" spans="1:18">
-      <c r="A91" s="23" t="s">
+      <c r="A91" s="12" t="s">
         <v>189</v>
       </c>
-      <c r="B91" s="23" t="s">
+      <c r="B91" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="C91" s="23" t="s">
+      <c r="C91" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D91" s="23" t="str">
+      <c r="D91" s="12" t="str">
         <f t="shared" si="3"/>
         <v>South</v>
       </c>
-      <c r="E91" s="23" t="s">
+      <c r="E91" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="F91" s="23" t="s">
+      <c r="F91" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G91" s="23" t="s">
+      <c r="G91" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="H91" s="23">
+      <c r="H91" s="12">
         <v>5460</v>
       </c>
-      <c r="I91" s="23">
+      <c r="I91" s="12">
         <v>37882</v>
       </c>
-      <c r="J91" s="23" t="s">
+      <c r="J91" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="K91" s="23" t="s">
+      <c r="K91" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="L91" s="23" t="s">
+      <c r="L91" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="M91" s="23">
+      <c r="M91" s="12">
         <v>3</v>
       </c>
-      <c r="N91" s="23">
+      <c r="N91" s="12">
         <v>13534</v>
       </c>
-      <c r="O91" s="23" t="s">
+      <c r="O91" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="P91" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q91" s="24" t="str">
+      <c r="P91" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q91" t="str">
         <f t="shared" si="4"/>
         <v>Not Achieved</v>
       </c>
@@ -6850,56 +6924,56 @@
       </c>
     </row>
     <row r="92" spans="1:18">
-      <c r="A92" s="23" t="s">
+      <c r="A92" s="12" t="s">
         <v>190</v>
       </c>
-      <c r="B92" s="23" t="s">
+      <c r="B92" s="12" t="s">
         <v>191</v>
       </c>
-      <c r="C92" s="23" t="s">
+      <c r="C92" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="D92" s="23" t="str">
+      <c r="D92" s="12" t="str">
         <f t="shared" si="3"/>
         <v>South</v>
       </c>
-      <c r="E92" s="23" t="s">
+      <c r="E92" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="F92" s="23" t="s">
+      <c r="F92" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G92" s="23" t="s">
+      <c r="G92" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="H92" s="23">
+      <c r="H92" s="12">
         <v>59140</v>
       </c>
-      <c r="I92" s="23">
+      <c r="I92" s="12">
         <v>37844</v>
       </c>
-      <c r="J92" s="23" t="s">
+      <c r="J92" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="K92" s="23" t="s">
+      <c r="K92" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="L92" s="23" t="s">
+      <c r="L92" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="M92" s="23">
+      <c r="M92" s="12">
         <v>27</v>
       </c>
-      <c r="N92" s="23">
+      <c r="N92" s="12">
         <v>16478</v>
       </c>
-      <c r="O92" s="23" t="s">
+      <c r="O92" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="P92" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q92" s="24" t="str">
+      <c r="P92" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q92" t="str">
         <f t="shared" si="4"/>
         <v>Achived</v>
       </c>
@@ -6909,54 +6983,54 @@
       </c>
     </row>
     <row r="93" spans="1:18">
-      <c r="A93" s="23" t="s">
+      <c r="A93" s="12" t="s">
         <v>192</v>
       </c>
-      <c r="B93" s="23" t="s">
+      <c r="B93" s="12" t="s">
         <v>193</v>
       </c>
-      <c r="C93" s="23" t="s">
+      <c r="C93" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="D93" s="23" t="str">
+      <c r="D93" s="12" t="str">
         <f t="shared" si="3"/>
         <v>West</v>
       </c>
-      <c r="E93" s="23" t="s">
+      <c r="E93" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="F93" s="23" t="s">
+      <c r="F93" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G93" s="23" t="s">
+      <c r="G93" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="H93" s="23">
+      <c r="H93" s="12">
         <v>36185</v>
       </c>
-      <c r="I93" s="23">
+      <c r="I93" s="12">
         <v>30235</v>
       </c>
-      <c r="J93" s="23" t="s">
+      <c r="J93" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="K93" s="23" t="s">
+      <c r="K93" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="L93" s="23" t="s">
+      <c r="L93" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="M93" s="23">
+      <c r="M93" s="12">
         <v>16</v>
       </c>
-      <c r="N93" s="23">
+      <c r="N93" s="12">
         <v>5634</v>
       </c>
-      <c r="O93" s="23" t="s">
+      <c r="O93" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="P93" s="23"/>
-      <c r="Q93" s="24" t="str">
+      <c r="P93" s="12"/>
+      <c r="Q93" t="str">
         <f t="shared" si="4"/>
         <v>Achived</v>
       </c>
@@ -6966,56 +7040,56 @@
       </c>
     </row>
     <row r="94" spans="1:18">
-      <c r="A94" s="23" t="s">
+      <c r="A94" s="12" t="s">
         <v>194</v>
       </c>
-      <c r="B94" s="23" t="s">
+      <c r="B94" s="12" t="s">
         <v>195</v>
       </c>
-      <c r="C94" s="23" t="s">
+      <c r="C94" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="D94" s="23" t="str">
+      <c r="D94" s="12" t="str">
         <f t="shared" si="3"/>
         <v>South</v>
       </c>
-      <c r="E94" s="23" t="s">
+      <c r="E94" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="F94" s="23" t="s">
+      <c r="F94" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G94" s="23" t="s">
+      <c r="G94" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="H94" s="23">
+      <c r="H94" s="12">
         <v>4399</v>
       </c>
-      <c r="I94" s="23">
+      <c r="I94" s="12">
         <v>23297</v>
       </c>
-      <c r="J94" s="23" t="s">
+      <c r="J94" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="K94" s="23" t="s">
+      <c r="K94" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="L94" s="23" t="s">
+      <c r="L94" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="M94" s="23">
+      <c r="M94" s="12">
         <v>0</v>
       </c>
-      <c r="N94" s="23">
+      <c r="N94" s="12">
         <v>11060</v>
       </c>
-      <c r="O94" s="23" t="s">
+      <c r="O94" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="P94" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q94" s="24" t="str">
+      <c r="P94" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q94" t="str">
         <f t="shared" si="4"/>
         <v>Not Achieved</v>
       </c>
@@ -7025,56 +7099,56 @@
       </c>
     </row>
     <row r="95" spans="1:18">
-      <c r="A95" s="23" t="s">
+      <c r="A95" s="12" t="s">
         <v>196</v>
       </c>
-      <c r="B95" s="23" t="s">
+      <c r="B95" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="C95" s="23" t="s">
+      <c r="C95" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="D95" s="23" t="str">
+      <c r="D95" s="12" t="str">
         <f t="shared" si="3"/>
         <v>South</v>
       </c>
-      <c r="E95" s="23" t="s">
+      <c r="E95" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="F95" s="23" t="s">
+      <c r="F95" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="G95" s="23" t="s">
+      <c r="G95" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="H95" s="23">
+      <c r="H95" s="12">
         <v>23358</v>
       </c>
-      <c r="I95" s="23">
+      <c r="I95" s="12">
         <v>29364</v>
       </c>
-      <c r="J95" s="23" t="s">
+      <c r="J95" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="K95" s="23" t="s">
+      <c r="K95" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="L95" s="23" t="s">
+      <c r="L95" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="M95" s="23">
+      <c r="M95" s="12">
         <v>3</v>
       </c>
-      <c r="N95" s="23">
+      <c r="N95" s="12">
         <v>8390</v>
       </c>
-      <c r="O95" s="23" t="s">
+      <c r="O95" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="P95" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q95" s="24" t="str">
+      <c r="P95" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q95" t="str">
         <f t="shared" si="4"/>
         <v>Not Achieved</v>
       </c>
@@ -7084,56 +7158,56 @@
       </c>
     </row>
     <row r="96" spans="1:18">
-      <c r="A96" s="23" t="s">
+      <c r="A96" s="12" t="s">
         <v>197</v>
       </c>
-      <c r="B96" s="23" t="s">
+      <c r="B96" s="12" t="s">
         <v>198</v>
       </c>
-      <c r="C96" s="23" t="s">
+      <c r="C96" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="D96" s="23" t="str">
+      <c r="D96" s="12" t="str">
         <f t="shared" si="3"/>
         <v>South</v>
       </c>
-      <c r="E96" s="23" t="s">
+      <c r="E96" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="F96" s="23" t="s">
+      <c r="F96" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G96" s="23" t="s">
+      <c r="G96" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="H96" s="23">
+      <c r="H96" s="12">
         <v>54838</v>
       </c>
-      <c r="I96" s="23">
+      <c r="I96" s="12">
         <v>52084</v>
       </c>
-      <c r="J96" s="23" t="s">
+      <c r="J96" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="K96" s="23" t="s">
+      <c r="K96" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="L96" s="23" t="s">
+      <c r="L96" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="M96" s="23">
+      <c r="M96" s="12">
         <v>25</v>
       </c>
-      <c r="N96" s="23">
+      <c r="N96" s="12">
         <v>5855</v>
       </c>
-      <c r="O96" s="23" t="s">
+      <c r="O96" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="P96" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q96" s="24" t="str">
+      <c r="P96" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q96" t="str">
         <f t="shared" si="4"/>
         <v>Achived</v>
       </c>
@@ -7143,56 +7217,56 @@
       </c>
     </row>
     <row r="97" spans="1:18">
-      <c r="A97" s="23" t="s">
+      <c r="A97" s="12" t="s">
         <v>199</v>
       </c>
-      <c r="B97" s="23" t="s">
+      <c r="B97" s="12" t="s">
         <v>200</v>
       </c>
-      <c r="C97" s="23" t="s">
+      <c r="C97" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="D97" s="23" t="str">
+      <c r="D97" s="12" t="str">
         <f t="shared" si="3"/>
         <v>North</v>
       </c>
-      <c r="E97" s="23" t="s">
+      <c r="E97" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="F97" s="23" t="s">
+      <c r="F97" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="G97" s="23" t="s">
+      <c r="G97" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="H97" s="23">
+      <c r="H97" s="12">
         <v>53461</v>
       </c>
-      <c r="I97" s="23">
+      <c r="I97" s="12">
         <v>18312</v>
       </c>
-      <c r="J97" s="23" t="s">
+      <c r="J97" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="K97" s="23" t="s">
+      <c r="K97" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="L97" s="23" t="s">
+      <c r="L97" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="M97" s="23">
+      <c r="M97" s="12">
         <v>3</v>
       </c>
-      <c r="N97" s="23">
+      <c r="N97" s="12">
         <v>2322</v>
       </c>
-      <c r="O97" s="23" t="s">
+      <c r="O97" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="P97" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q97" s="24" t="str">
+      <c r="P97" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q97" t="str">
         <f t="shared" si="4"/>
         <v>Achived</v>
       </c>
@@ -7202,56 +7276,56 @@
       </c>
     </row>
     <row r="98" spans="1:18">
-      <c r="A98" s="23" t="s">
+      <c r="A98" s="12" t="s">
         <v>201</v>
       </c>
-      <c r="B98" s="23" t="s">
+      <c r="B98" s="12" t="s">
         <v>202</v>
       </c>
-      <c r="C98" s="23" t="s">
+      <c r="C98" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="D98" s="23" t="str">
+      <c r="D98" s="12" t="str">
         <f t="shared" si="3"/>
         <v>South</v>
       </c>
-      <c r="E98" s="23" t="s">
+      <c r="E98" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="F98" s="23" t="s">
+      <c r="F98" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="G98" s="23" t="s">
+      <c r="G98" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="H98" s="23">
+      <c r="H98" s="12">
         <v>42581</v>
       </c>
-      <c r="I98" s="23">
+      <c r="I98" s="12">
         <v>37737</v>
       </c>
-      <c r="J98" s="23" t="s">
+      <c r="J98" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="K98" s="23" t="s">
+      <c r="K98" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="L98" s="23" t="s">
+      <c r="L98" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="M98" s="23">
+      <c r="M98" s="12">
         <v>28</v>
       </c>
-      <c r="N98" s="23">
+      <c r="N98" s="12">
         <v>4939</v>
       </c>
-      <c r="O98" s="23" t="s">
+      <c r="O98" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="P98" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q98" s="24" t="str">
+      <c r="P98" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q98" t="str">
         <f t="shared" si="4"/>
         <v>Achived</v>
       </c>
@@ -7261,56 +7335,56 @@
       </c>
     </row>
     <row r="99" spans="1:18">
-      <c r="A99" s="23" t="s">
+      <c r="A99" s="12" t="s">
         <v>203</v>
       </c>
-      <c r="B99" s="23" t="s">
+      <c r="B99" s="12" t="s">
         <v>204</v>
       </c>
-      <c r="C99" s="23" t="s">
+      <c r="C99" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="D99" s="23" t="str">
+      <c r="D99" s="12" t="str">
         <f t="shared" si="3"/>
         <v>North</v>
       </c>
-      <c r="E99" s="23" t="s">
+      <c r="E99" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="F99" s="23" t="s">
+      <c r="F99" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="G99" s="23" t="s">
+      <c r="G99" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="H99" s="23">
+      <c r="H99" s="12">
         <v>43601</v>
       </c>
-      <c r="I99" s="23">
+      <c r="I99" s="12">
         <v>22897</v>
       </c>
-      <c r="J99" s="23" t="s">
+      <c r="J99" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="K99" s="23" t="s">
+      <c r="K99" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="L99" s="23" t="s">
+      <c r="L99" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="M99" s="23">
+      <c r="M99" s="12">
         <v>19</v>
       </c>
-      <c r="N99" s="23">
+      <c r="N99" s="12">
         <v>17302</v>
       </c>
-      <c r="O99" s="23" t="s">
+      <c r="O99" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="P99" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q99" s="24" t="str">
+      <c r="P99" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q99" t="str">
         <f t="shared" si="4"/>
         <v>Achived</v>
       </c>
@@ -7320,56 +7394,56 @@
       </c>
     </row>
     <row r="100" spans="1:18">
-      <c r="A100" s="23" t="s">
+      <c r="A100" s="12" t="s">
         <v>205</v>
       </c>
-      <c r="B100" s="23" t="s">
+      <c r="B100" s="12" t="s">
         <v>206</v>
       </c>
-      <c r="C100" s="23" t="s">
+      <c r="C100" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="D100" s="23" t="str">
+      <c r="D100" s="12" t="str">
         <f t="shared" si="3"/>
         <v>North</v>
       </c>
-      <c r="E100" s="23" t="s">
+      <c r="E100" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="F100" s="23" t="s">
+      <c r="F100" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G100" s="23" t="s">
+      <c r="G100" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="H100" s="23">
+      <c r="H100" s="12">
         <v>1683</v>
       </c>
-      <c r="I100" s="23">
+      <c r="I100" s="12">
         <v>18272</v>
       </c>
-      <c r="J100" s="23" t="s">
+      <c r="J100" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="K100" s="23" t="s">
+      <c r="K100" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="L100" s="23" t="s">
+      <c r="L100" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="M100" s="23">
+      <c r="M100" s="12">
         <v>10</v>
       </c>
-      <c r="N100" s="23">
+      <c r="N100" s="12">
         <v>13325</v>
       </c>
-      <c r="O100" s="23" t="s">
+      <c r="O100" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="P100" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q100" s="24" t="str">
+      <c r="P100" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q100" t="str">
         <f t="shared" si="4"/>
         <v>Not Achieved</v>
       </c>
@@ -7379,56 +7453,56 @@
       </c>
     </row>
     <row r="101" spans="1:18">
-      <c r="A101" s="23" t="s">
+      <c r="A101" s="12" t="s">
         <v>207</v>
       </c>
-      <c r="B101" s="23" t="s">
+      <c r="B101" s="12" t="s">
         <v>208</v>
       </c>
-      <c r="C101" s="23" t="s">
+      <c r="C101" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="D101" s="23" t="str">
+      <c r="D101" s="12" t="str">
         <f t="shared" si="3"/>
         <v>South</v>
       </c>
-      <c r="E101" s="23" t="s">
+      <c r="E101" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="F101" s="23" t="s">
+      <c r="F101" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G101" s="23" t="s">
+      <c r="G101" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="H101" s="23">
+      <c r="H101" s="12">
         <v>12349</v>
       </c>
-      <c r="I101" s="23">
+      <c r="I101" s="12">
         <v>28485</v>
       </c>
-      <c r="J101" s="23" t="s">
+      <c r="J101" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="K101" s="23" t="s">
+      <c r="K101" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="L101" s="23" t="s">
+      <c r="L101" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="M101" s="23">
+      <c r="M101" s="12">
         <v>28</v>
       </c>
-      <c r="N101" s="23">
+      <c r="N101" s="12">
         <v>14015</v>
       </c>
-      <c r="O101" s="23" t="s">
+      <c r="O101" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="P101" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q101" s="24" t="str">
+      <c r="P101" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q101" t="str">
         <f t="shared" si="4"/>
         <v>Not Achieved</v>
       </c>
@@ -7438,56 +7512,56 @@
       </c>
     </row>
     <row r="102" spans="1:18">
-      <c r="A102" s="23" t="s">
+      <c r="A102" s="12" t="s">
         <v>209</v>
       </c>
-      <c r="B102" s="23" t="s">
+      <c r="B102" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="C102" s="23" t="s">
+      <c r="C102" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="D102" s="23" t="str">
+      <c r="D102" s="12" t="str">
         <f t="shared" si="3"/>
         <v>South</v>
       </c>
-      <c r="E102" s="23" t="s">
+      <c r="E102" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="F102" s="23" t="s">
+      <c r="F102" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G102" s="23" t="s">
+      <c r="G102" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="H102" s="23">
+      <c r="H102" s="12">
         <v>39775</v>
       </c>
-      <c r="I102" s="23">
+      <c r="I102" s="12">
         <v>46900</v>
       </c>
-      <c r="J102" s="23" t="s">
+      <c r="J102" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="K102" s="23" t="s">
+      <c r="K102" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="L102" s="23" t="s">
+      <c r="L102" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="M102" s="23">
+      <c r="M102" s="12">
         <v>22</v>
       </c>
-      <c r="N102" s="23">
+      <c r="N102" s="12">
         <v>19870</v>
       </c>
-      <c r="O102" s="23" t="s">
+      <c r="O102" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="P102" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q102" s="24" t="str">
+      <c r="P102" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q102" t="str">
         <f t="shared" si="4"/>
         <v>Not Achieved</v>
       </c>
@@ -7610,7 +7684,7 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="1"/>
-      <c r="B18" s="21" t="s">
+      <c r="B18" s="24" t="s">
         <v>224</v>
       </c>
       <c r="C18" s="6" t="s">
@@ -7619,14 +7693,14 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="1"/>
-      <c r="B19" s="21"/>
+      <c r="B19" s="24"/>
       <c r="C19" s="6" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="1"/>
-      <c r="B20" s="21" t="s">
+      <c r="B20" s="24" t="s">
         <v>227</v>
       </c>
       <c r="C20" s="6" t="s">
@@ -7635,14 +7709,14 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="1"/>
-      <c r="B21" s="21"/>
+      <c r="B21" s="24"/>
       <c r="C21" s="6" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="1"/>
-      <c r="B22" s="21" t="s">
+      <c r="B22" s="24" t="s">
         <v>230</v>
       </c>
       <c r="C22" s="6" t="s">
@@ -7651,14 +7725,14 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="1"/>
-      <c r="B23" s="21"/>
+      <c r="B23" s="24"/>
       <c r="C23" s="6" t="s">
         <v>232</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="1"/>
-      <c r="B24" s="21" t="s">
+      <c r="B24" s="24" t="s">
         <v>233</v>
       </c>
       <c r="C24" s="7" t="s">
@@ -7667,7 +7741,7 @@
     </row>
     <row r="25" spans="1:3" ht="15" thickBot="1">
       <c r="A25" s="1"/>
-      <c r="B25" s="22"/>
+      <c r="B25" s="25"/>
       <c r="C25" s="8" t="s">
         <v>235</v>
       </c>
@@ -7705,25 +7779,25 @@
   </cols>
   <sheetData>
     <row r="4" spans="3:9">
-      <c r="C4" s="25" t="s">
+      <c r="C4" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="25" t="s">
+      <c r="D4" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="25" t="s">
+      <c r="E4" s="20" t="s">
         <v>240</v>
       </c>
-      <c r="F4" s="25" t="s">
+      <c r="F4" s="20" t="s">
         <v>242</v>
       </c>
-      <c r="G4" s="26" t="s">
+      <c r="G4" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="26" t="s">
+      <c r="H4" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="I4" s="26" t="s">
+      <c r="I4" s="21" t="s">
         <v>247</v>
       </c>
     </row>
@@ -7740,15 +7814,15 @@
       <c r="F5" s="12">
         <v>1</v>
       </c>
-      <c r="G5" s="23" t="s">
+      <c r="G5" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="H5" s="23" t="s">
+      <c r="H5" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="I5" t="str" cm="1">
-        <f t="array" ref="I5:I15">IF(Sales&gt;=Target_Values,"Achieved","Not Achevied")</f>
-        <v>Achieved</v>
+      <c r="I5" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="I5" ca="1">IF(Sales&gt;=Target_Values,"Achieved","Not Achevied")</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="6" spans="3:9">
@@ -7764,14 +7838,11 @@
       <c r="F6" s="12">
         <v>3</v>
       </c>
-      <c r="G6" s="23" t="s">
+      <c r="G6" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="H6" s="23" t="s">
+      <c r="H6" s="12" t="s">
         <v>30</v>
-      </c>
-      <c r="I6" t="str">
-        <v>Not Achevied</v>
       </c>
     </row>
     <row r="7" spans="3:9">
@@ -7787,14 +7858,11 @@
       <c r="F7" s="12">
         <v>2</v>
       </c>
-      <c r="G7" s="23" t="s">
+      <c r="G7" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="H7" s="23" t="s">
+      <c r="H7" s="12" t="s">
         <v>30</v>
-      </c>
-      <c r="I7" t="str">
-        <v>Not Achevied</v>
       </c>
     </row>
     <row r="8" spans="3:9">
@@ -7810,14 +7878,11 @@
       <c r="F8" s="12">
         <v>4</v>
       </c>
-      <c r="G8" s="23" t="s">
+      <c r="G8" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="H8" s="23" t="s">
+      <c r="H8" s="12" t="s">
         <v>30</v>
-      </c>
-      <c r="I8" t="str">
-        <v>Achieved</v>
       </c>
     </row>
     <row r="9" spans="3:9">
@@ -7833,14 +7898,11 @@
       <c r="F9" s="12">
         <v>5</v>
       </c>
-      <c r="G9" s="23" t="s">
+      <c r="G9" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="H9" s="23" t="s">
+      <c r="H9" s="12" t="s">
         <v>30</v>
-      </c>
-      <c r="I9" t="str">
-        <v>Not Achevied</v>
       </c>
     </row>
     <row r="10" spans="3:9">
@@ -7856,14 +7918,11 @@
       <c r="F10" s="12">
         <v>66</v>
       </c>
-      <c r="G10" s="23" t="s">
+      <c r="G10" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="H10" s="23" t="s">
+      <c r="H10" s="12" t="s">
         <v>21</v>
-      </c>
-      <c r="I10" t="str">
-        <v>Not Achevied</v>
       </c>
     </row>
     <row r="11" spans="3:9">
@@ -7879,14 +7938,11 @@
       <c r="F11" s="12">
         <v>77</v>
       </c>
-      <c r="G11" s="23" t="s">
+      <c r="G11" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="H11" s="23" t="s">
+      <c r="H11" s="12" t="s">
         <v>21</v>
-      </c>
-      <c r="I11" t="str">
-        <v>Not Achevied</v>
       </c>
     </row>
     <row r="12" spans="3:9">
@@ -7902,14 +7958,11 @@
       <c r="F12" s="12">
         <v>16</v>
       </c>
-      <c r="G12" s="23" t="s">
+      <c r="G12" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="H12" s="23" t="s">
+      <c r="H12" s="12" t="s">
         <v>21</v>
-      </c>
-      <c r="I12" t="str">
-        <v>Achieved</v>
       </c>
     </row>
     <row r="13" spans="3:9">
@@ -7925,14 +7978,11 @@
       <c r="F13" s="12">
         <v>8</v>
       </c>
-      <c r="G13" s="23" t="s">
+      <c r="G13" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="H13" s="23" t="s">
+      <c r="H13" s="12" t="s">
         <v>21</v>
-      </c>
-      <c r="I13" t="str">
-        <v>Achieved</v>
       </c>
     </row>
     <row r="14" spans="3:9">
@@ -7948,14 +7998,11 @@
       <c r="F14" s="12">
         <v>1</v>
       </c>
-      <c r="G14" s="23" t="s">
+      <c r="G14" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="H14" s="23" t="s">
+      <c r="H14" s="12" t="s">
         <v>30</v>
-      </c>
-      <c r="I14" t="str">
-        <v>Achieved</v>
       </c>
     </row>
     <row r="15" spans="3:9">
@@ -7971,18 +8018,15 @@
       <c r="F15" s="12">
         <v>2</v>
       </c>
-      <c r="G15" s="27" t="s">
+      <c r="G15" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="H15" s="23" t="s">
+      <c r="H15" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="I15" t="str">
-        <v>Achieved</v>
-      </c>
-    </row>
-    <row r="16" spans="3:9">
-      <c r="G16" s="28"/>
+      <c r="I15">
+        <v>9</v>
+      </c>
     </row>
     <row r="17" spans="3:9">
       <c r="C17" t="s">
@@ -8010,10 +8054,10 @@
       </c>
     </row>
     <row r="20" spans="3:9">
-      <c r="D20" s="20" t="s">
+      <c r="D20" s="26" t="s">
         <v>244</v>
       </c>
-      <c r="E20" s="20"/>
+      <c r="E20" s="26"/>
     </row>
     <row r="21" spans="3:9">
       <c r="D21" t="str">
@@ -8100,12 +8144,12 @@
       </c>
     </row>
     <row r="32" spans="3:9">
-      <c r="D32" s="29" t="s">
+      <c r="D32" s="23" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="33" spans="4:7">
-      <c r="D33" s="23" t="s">
+      <c r="D33" s="12" t="s">
         <v>19</v>
       </c>
       <c r="E33" t="s">
@@ -8117,7 +8161,7 @@
       </c>
     </row>
     <row r="34" spans="4:7">
-      <c r="D34" s="23" t="s">
+      <c r="D34" s="12" t="s">
         <v>29</v>
       </c>
     </row>
@@ -8138,7 +8182,7 @@
       </c>
     </row>
     <row r="37" spans="4:7">
-      <c r="D37" s="23" t="s">
+      <c r="D37" s="12" t="s">
         <v>21</v>
       </c>
       <c r="E37" t="s">
@@ -8154,7 +8198,7 @@
       </c>
     </row>
     <row r="38" spans="4:7">
-      <c r="D38" s="23" t="s">
+      <c r="D38" s="12" t="s">
         <v>30</v>
       </c>
     </row>
@@ -8166,13 +8210,13 @@
     <row r="40" spans="4:7">
       <c r="G40">
         <f ca="1">SUMIFS(C:C,I:I,"Achieved")</f>
-        <v>286552</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="4:7">
       <c r="G41">
         <f ca="1">SUMIFS(C:C,I:I,"Not Achevied")</f>
-        <v>64220</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
